--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,60 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -731,35 +731,38 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2523700</v>
+        <v>2417800</v>
       </c>
       <c r="E8" s="3">
-        <v>5388100</v>
+        <v>2530900</v>
       </c>
       <c r="F8" s="3">
-        <v>2738500</v>
+        <v>5403500</v>
       </c>
       <c r="G8" s="3">
-        <v>2720100</v>
+        <v>2746400</v>
       </c>
       <c r="H8" s="3">
-        <v>3224600</v>
+        <v>2727900</v>
       </c>
       <c r="I8" s="3">
-        <v>6587000</v>
+        <v>3233800</v>
       </c>
       <c r="J8" s="3">
+        <v>6605900</v>
+      </c>
+      <c r="K8" s="3">
         <v>3132400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -781,35 +784,38 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1991000</v>
+        <v>1955300</v>
       </c>
       <c r="E9" s="3">
-        <v>4255400</v>
+        <v>1996700</v>
       </c>
       <c r="F9" s="3">
-        <v>2193900</v>
+        <v>4267500</v>
       </c>
       <c r="G9" s="3">
-        <v>2310000</v>
+        <v>2200100</v>
       </c>
       <c r="H9" s="3">
-        <v>2556300</v>
+        <v>2316600</v>
       </c>
       <c r="I9" s="3">
-        <v>4866200</v>
+        <v>2563600</v>
       </c>
       <c r="J9" s="3">
+        <v>4880100</v>
+      </c>
+      <c r="K9" s="3">
         <v>2316500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,35 +837,38 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>532700</v>
+        <v>462400</v>
       </c>
       <c r="E10" s="3">
-        <v>1132700</v>
+        <v>534300</v>
       </c>
       <c r="F10" s="3">
-        <v>544700</v>
+        <v>1136000</v>
       </c>
       <c r="G10" s="3">
-        <v>410100</v>
+        <v>546200</v>
       </c>
       <c r="H10" s="3">
-        <v>668400</v>
+        <v>411300</v>
       </c>
       <c r="I10" s="3">
-        <v>1720800</v>
+        <v>670300</v>
       </c>
       <c r="J10" s="3">
+        <v>1725700</v>
+      </c>
+      <c r="K10" s="3">
         <v>815900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -881,8 +890,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -901,35 +913,36 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>73800</v>
+        <v>77300</v>
       </c>
       <c r="E12" s="3">
-        <v>147600</v>
+        <v>74000</v>
       </c>
       <c r="F12" s="3">
-        <v>76000</v>
+        <v>148000</v>
       </c>
       <c r="G12" s="3">
-        <v>77000</v>
+        <v>76200</v>
       </c>
       <c r="H12" s="3">
+        <v>77300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>71800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>144700</v>
+      </c>
+      <c r="K12" s="3">
         <v>71600</v>
       </c>
-      <c r="I12" s="3">
-        <v>144300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>71600</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,8 +964,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,35 +1017,38 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>34700</v>
+        <v>76200</v>
       </c>
       <c r="E14" s="3">
-        <v>42300</v>
+        <v>34800</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>93600</v>
       </c>
       <c r="G14" s="3">
-        <v>77000</v>
+        <v>7600</v>
       </c>
       <c r="H14" s="3">
-        <v>7600</v>
+        <v>50100</v>
       </c>
       <c r="I14" s="3">
-        <v>46700</v>
+        <v>16300</v>
       </c>
       <c r="J14" s="3">
+        <v>101200</v>
+      </c>
+      <c r="K14" s="3">
         <v>4300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1070,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1083,8 +1105,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1101,8 +1123,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1118,35 +1143,36 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2326200</v>
+        <v>2328500</v>
       </c>
       <c r="E17" s="3">
-        <v>4935700</v>
+        <v>2332900</v>
       </c>
       <c r="F17" s="3">
-        <v>2525900</v>
+        <v>4949800</v>
       </c>
       <c r="G17" s="3">
-        <v>2700600</v>
+        <v>2533100</v>
       </c>
       <c r="H17" s="3">
-        <v>2876300</v>
+        <v>2708300</v>
       </c>
       <c r="I17" s="3">
-        <v>5558500</v>
+        <v>2884600</v>
       </c>
       <c r="J17" s="3">
+        <v>5574300</v>
+      </c>
+      <c r="K17" s="3">
         <v>2661500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,35 +1194,38 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>197500</v>
+        <v>89200</v>
       </c>
       <c r="E18" s="3">
-        <v>452400</v>
+        <v>198000</v>
       </c>
       <c r="F18" s="3">
-        <v>212700</v>
+        <v>453700</v>
       </c>
       <c r="G18" s="3">
-        <v>19500</v>
+        <v>213300</v>
       </c>
       <c r="H18" s="3">
-        <v>348300</v>
+        <v>19600</v>
       </c>
       <c r="I18" s="3">
-        <v>1028600</v>
+        <v>349300</v>
       </c>
       <c r="J18" s="3">
+        <v>1031500</v>
+      </c>
+      <c r="K18" s="3">
         <v>470900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1218,8 +1247,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1238,35 +1270,36 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11900</v>
+        <v>-30500</v>
       </c>
       <c r="E20" s="3">
-        <v>-43400</v>
+        <v>-12000</v>
       </c>
       <c r="F20" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-23900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-34700</v>
-      </c>
       <c r="H20" s="3">
-        <v>-21700</v>
+        <v>-34800</v>
       </c>
       <c r="I20" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-16300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,25 +1321,28 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>378700</v>
+        <v>282900</v>
       </c>
       <c r="E21" s="3">
-        <v>771400</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3">
-        <v>751900</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+        <v>379700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>773600</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3">
+        <v>754100</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1338,8 +1374,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1370,8 +1409,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1388,35 +1427,38 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>185500</v>
+        <v>58800</v>
       </c>
       <c r="E23" s="3">
-        <v>409000</v>
+        <v>186100</v>
       </c>
       <c r="F23" s="3">
-        <v>188800</v>
+        <v>410200</v>
       </c>
       <c r="G23" s="3">
+        <v>189300</v>
+      </c>
+      <c r="H23" s="3">
         <v>-15200</v>
       </c>
-      <c r="H23" s="3">
-        <v>326600</v>
-      </c>
       <c r="I23" s="3">
-        <v>1012300</v>
+        <v>327500</v>
       </c>
       <c r="J23" s="3">
+        <v>1015200</v>
+      </c>
+      <c r="K23" s="3">
         <v>461100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,35 +1480,38 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>58600</v>
+        <v>33700</v>
       </c>
       <c r="E24" s="3">
-        <v>99800</v>
+        <v>58800</v>
       </c>
       <c r="F24" s="3">
-        <v>44500</v>
+        <v>100100</v>
       </c>
       <c r="G24" s="3">
+        <v>44600</v>
+      </c>
+      <c r="H24" s="3">
         <v>-25000</v>
       </c>
-      <c r="H24" s="3">
-        <v>82500</v>
-      </c>
       <c r="I24" s="3">
-        <v>218100</v>
+        <v>82700</v>
       </c>
       <c r="J24" s="3">
+        <v>218700</v>
+      </c>
+      <c r="K24" s="3">
         <v>103100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1488,8 +1533,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1538,35 +1586,38 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>126900</v>
+        <v>25000</v>
       </c>
       <c r="E26" s="3">
-        <v>309200</v>
+        <v>127300</v>
       </c>
       <c r="F26" s="3">
-        <v>144300</v>
+        <v>310100</v>
       </c>
       <c r="G26" s="3">
+        <v>144700</v>
+      </c>
+      <c r="H26" s="3">
         <v>9800</v>
       </c>
-      <c r="H26" s="3">
-        <v>244100</v>
-      </c>
       <c r="I26" s="3">
-        <v>794200</v>
+        <v>244800</v>
       </c>
       <c r="J26" s="3">
+        <v>796500</v>
+      </c>
+      <c r="K26" s="3">
         <v>358100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,35 +1639,38 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>123700</v>
+        <v>4400</v>
       </c>
       <c r="E27" s="3">
-        <v>302700</v>
+        <v>124000</v>
       </c>
       <c r="F27" s="3">
-        <v>143200</v>
+        <v>303600</v>
       </c>
       <c r="G27" s="3">
+        <v>143600</v>
+      </c>
+      <c r="H27" s="3">
         <v>-5400</v>
       </c>
-      <c r="H27" s="3">
-        <v>243000</v>
-      </c>
       <c r="I27" s="3">
-        <v>786600</v>
+        <v>243700</v>
       </c>
       <c r="J27" s="3">
+        <v>788900</v>
+      </c>
+      <c r="K27" s="3">
         <v>357000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1638,8 +1692,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1688,8 +1745,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1720,8 +1780,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
@@ -1738,8 +1798,11 @@
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1788,8 +1851,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1838,35 +1904,38 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11900</v>
+        <v>30500</v>
       </c>
       <c r="E32" s="3">
-        <v>43400</v>
+        <v>12000</v>
       </c>
       <c r="F32" s="3">
+        <v>43500</v>
+      </c>
+      <c r="G32" s="3">
         <v>23900</v>
       </c>
-      <c r="G32" s="3">
-        <v>34700</v>
-      </c>
       <c r="H32" s="3">
-        <v>21700</v>
+        <v>34800</v>
       </c>
       <c r="I32" s="3">
+        <v>21800</v>
+      </c>
+      <c r="J32" s="3">
         <v>16300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1888,35 +1957,38 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>123700</v>
+        <v>4400</v>
       </c>
       <c r="E33" s="3">
-        <v>302700</v>
+        <v>124000</v>
       </c>
       <c r="F33" s="3">
-        <v>143200</v>
+        <v>303600</v>
       </c>
       <c r="G33" s="3">
+        <v>143600</v>
+      </c>
+      <c r="H33" s="3">
         <v>-5400</v>
       </c>
-      <c r="H33" s="3">
-        <v>243000</v>
-      </c>
       <c r="I33" s="3">
-        <v>786600</v>
+        <v>243700</v>
       </c>
       <c r="J33" s="3">
+        <v>788900</v>
+      </c>
+      <c r="K33" s="3">
         <v>357000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1938,8 +2010,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1988,35 +2063,38 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>123700</v>
+        <v>4400</v>
       </c>
       <c r="E35" s="3">
-        <v>302700</v>
+        <v>124000</v>
       </c>
       <c r="F35" s="3">
-        <v>143200</v>
+        <v>303600</v>
       </c>
       <c r="G35" s="3">
+        <v>143600</v>
+      </c>
+      <c r="H35" s="3">
         <v>-5400</v>
       </c>
-      <c r="H35" s="3">
-        <v>243000</v>
-      </c>
       <c r="I35" s="3">
-        <v>786600</v>
+        <v>243700</v>
       </c>
       <c r="J35" s="3">
+        <v>788900</v>
+      </c>
+      <c r="K35" s="3">
         <v>357000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,40 +2116,43 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2174,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2113,8 +2197,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2133,19 +2218,20 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2061500</v>
+        <v>2225200</v>
       </c>
       <c r="E41" s="3">
-        <v>1807600</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+        <v>2067400</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1812800</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -2162,11 +2248,11 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
@@ -2183,19 +2269,22 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E42" s="3">
         <v>14100</v>
       </c>
-      <c r="E42" s="3">
-        <v>46700</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+      <c r="F42" s="3">
+        <v>46800</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -2212,11 +2301,11 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2233,19 +2322,22 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1841200</v>
+        <v>1711600</v>
       </c>
       <c r="E43" s="3">
-        <v>1942200</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+        <v>1846500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1947700</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -2262,11 +2354,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2283,19 +2375,22 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1461500</v>
+        <v>1314400</v>
       </c>
       <c r="E44" s="3">
-        <v>1496200</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
+        <v>1465700</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1500500</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -2312,11 +2407,11 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
@@ -2333,8 +2428,11 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2365,8 +2463,8 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2383,19 +2481,22 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5378300</v>
+        <v>5286000</v>
       </c>
       <c r="E46" s="3">
-        <v>5292600</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
+        <v>5393700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5307800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -2412,11 +2513,11 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
+        <v>0</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
@@ -2433,19 +2534,22 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>73800</v>
+        <v>70700</v>
       </c>
       <c r="E47" s="3">
-        <v>76000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+        <v>74000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>76200</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -2462,11 +2566,11 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
@@ -2483,19 +2587,22 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3725900</v>
+        <v>4058600</v>
       </c>
       <c r="E48" s="3">
-        <v>3649900</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>3736500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3660400</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -2512,11 +2619,11 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2533,19 +2640,22 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5216700</v>
+        <v>5936700</v>
       </c>
       <c r="E49" s="3">
-        <v>5191700</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+        <v>5231600</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5206600</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -2562,11 +2672,11 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2583,8 +2693,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2633,8 +2746,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2683,19 +2799,22 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>434000</v>
+        <v>443900</v>
       </c>
       <c r="E52" s="3">
-        <v>454600</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+        <v>435200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>455900</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -2712,11 +2831,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2733,8 +2852,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2783,19 +2905,22 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14828700</v>
+        <v>15795900</v>
       </c>
       <c r="E54" s="3">
-        <v>14664900</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>14871100</v>
+      </c>
+      <c r="F54" s="3">
+        <v>14706800</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2812,11 +2937,11 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
@@ -2833,8 +2958,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2853,8 +2981,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2873,19 +3002,20 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1026400</v>
+        <v>1127300</v>
       </c>
       <c r="E57" s="3">
-        <v>1082800</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>1029300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1085900</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2902,11 +3032,11 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2923,19 +3053,22 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>720400</v>
+        <v>588700</v>
       </c>
       <c r="E58" s="3">
-        <v>716100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+        <v>722500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>718100</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2952,11 +3085,11 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2973,19 +3106,22 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>644500</v>
+        <v>546200</v>
       </c>
       <c r="E59" s="3">
-        <v>611900</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>646300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>613700</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -3002,11 +3138,11 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
@@ -3023,19 +3159,22 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2391300</v>
+        <v>2262200</v>
       </c>
       <c r="E60" s="3">
-        <v>2410900</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
+        <v>2398200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2417800</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -3052,11 +3191,11 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -3073,19 +3212,22 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3206200</v>
+        <v>4063000</v>
       </c>
       <c r="E61" s="3">
-        <v>3201800</v>
+        <v>3215300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3211000</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -3123,19 +3265,22 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1211900</v>
+        <v>1359000</v>
       </c>
       <c r="E62" s="3">
-        <v>1271600</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>1215400</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1275300</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -3152,11 +3297,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3173,8 +3318,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3223,8 +3371,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3273,8 +3424,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3323,19 +3477,22 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6853900</v>
+        <v>7958400</v>
       </c>
       <c r="E66" s="3">
-        <v>6926600</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>6873500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>6946400</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -3352,11 +3509,11 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
+        <v>0</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
@@ -3373,8 +3530,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3393,8 +3553,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3443,8 +3604,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3493,8 +3657,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3525,8 +3692,8 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
+      <c r="M70" s="3">
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>3</v>
@@ -3543,8 +3710,11 @@
       <c r="R70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3593,19 +3763,22 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4953000</v>
+        <v>4936700</v>
       </c>
       <c r="E72" s="3">
-        <v>4825000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+        <v>4967200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>4838800</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -3622,11 +3795,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
@@ -3643,8 +3816,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3693,8 +3869,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3743,8 +3922,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3793,19 +3975,22 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7974800</v>
+        <v>7837600</v>
       </c>
       <c r="E76" s="3">
-        <v>7738200</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+        <v>7997500</v>
+      </c>
+      <c r="F76" s="3">
+        <v>7760300</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -3822,11 +4007,11 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
+        <v>0</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
@@ -3843,8 +4028,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3893,40 +4081,43 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3948,35 +4139,38 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>123700</v>
+        <v>4400</v>
       </c>
       <c r="E81" s="3">
-        <v>302700</v>
+        <v>124000</v>
       </c>
       <c r="F81" s="3">
-        <v>143200</v>
+        <v>303600</v>
       </c>
       <c r="G81" s="3">
+        <v>143600</v>
+      </c>
+      <c r="H81" s="3">
         <v>-5400</v>
       </c>
-      <c r="H81" s="3">
-        <v>243000</v>
-      </c>
       <c r="I81" s="3">
-        <v>786600</v>
+        <v>243700</v>
       </c>
       <c r="J81" s="3">
+        <v>788900</v>
+      </c>
+      <c r="K81" s="3">
         <v>357000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4192,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4018,19 +4215,20 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>193100</v>
+        <v>224100</v>
       </c>
       <c r="E83" s="3">
-        <v>362400</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+        <v>193700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>363400</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -4044,14 +4242,14 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -4068,8 +4266,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4118,8 +4319,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4168,8 +4372,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4218,8 +4425,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4268,8 +4478,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4318,19 +4531,22 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>426400</v>
+        <v>502700</v>
       </c>
       <c r="E89" s="3">
-        <v>452400</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>427600</v>
+      </c>
+      <c r="F89" s="3">
+        <v>453700</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -4344,14 +4560,14 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
@@ -4368,8 +4584,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4388,17 +4607,18 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-181000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-149000</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -4420,8 +4640,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4438,8 +4658,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4488,8 +4711,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4538,19 +4764,22 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-135600</v>
+        <v>-917300</v>
       </c>
       <c r="E94" s="3">
-        <v>-419900</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>-136000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-421100</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -4564,14 +4793,14 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -4588,8 +4817,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4608,8 +4840,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4617,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-274500</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-275300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4658,8 +4891,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4708,8 +4944,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4758,8 +4997,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4808,19 +5050,22 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-41200</v>
+        <v>562500</v>
       </c>
       <c r="E100" s="3">
-        <v>40100</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>-41300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>40300</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -4834,14 +5079,14 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
@@ -4858,20 +5103,23 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4300</v>
+        <v>9800</v>
       </c>
       <c r="E101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F101" s="3">
         <v>7600</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,14 +5132,14 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4908,19 +5156,22 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>253900</v>
+        <v>157800</v>
       </c>
       <c r="E102" s="3">
-        <v>80300</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
+        <v>254600</v>
+      </c>
+      <c r="F102" s="3">
+        <v>80500</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>
@@ -4934,14 +5185,14 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4956,6 +5207,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -734,38 +735,41 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2417800</v>
+        <v>2529900</v>
       </c>
       <c r="E8" s="3">
-        <v>2530900</v>
+        <v>2401300</v>
       </c>
       <c r="F8" s="3">
-        <v>5403500</v>
+        <v>2513700</v>
       </c>
       <c r="G8" s="3">
-        <v>2746400</v>
+        <v>5366800</v>
       </c>
       <c r="H8" s="3">
-        <v>2727900</v>
+        <v>2727700</v>
       </c>
       <c r="I8" s="3">
-        <v>3233800</v>
+        <v>2709300</v>
       </c>
       <c r="J8" s="3">
+        <v>3211800</v>
+      </c>
+      <c r="K8" s="3">
         <v>6605900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3132400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -787,38 +791,41 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1955300</v>
+        <v>2024200</v>
       </c>
       <c r="E9" s="3">
-        <v>1996700</v>
+        <v>1942000</v>
       </c>
       <c r="F9" s="3">
-        <v>4267500</v>
+        <v>1983100</v>
       </c>
       <c r="G9" s="3">
-        <v>2200100</v>
+        <v>4238500</v>
       </c>
       <c r="H9" s="3">
-        <v>2316600</v>
+        <v>2185200</v>
       </c>
       <c r="I9" s="3">
-        <v>2563600</v>
+        <v>2300800</v>
       </c>
       <c r="J9" s="3">
+        <v>2546100</v>
+      </c>
+      <c r="K9" s="3">
         <v>4880100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2316500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -840,38 +847,41 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>462400</v>
+        <v>505800</v>
       </c>
       <c r="E10" s="3">
-        <v>534300</v>
+        <v>459300</v>
       </c>
       <c r="F10" s="3">
-        <v>1136000</v>
+        <v>530600</v>
       </c>
       <c r="G10" s="3">
-        <v>546200</v>
+        <v>1128300</v>
       </c>
       <c r="H10" s="3">
-        <v>411300</v>
+        <v>542500</v>
       </c>
       <c r="I10" s="3">
-        <v>670300</v>
+        <v>408500</v>
       </c>
       <c r="J10" s="3">
+        <v>665700</v>
+      </c>
+      <c r="K10" s="3">
         <v>1725700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>815900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -893,8 +903,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -914,38 +927,39 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>77300</v>
+        <v>74600</v>
       </c>
       <c r="E12" s="3">
-        <v>74000</v>
+        <v>76700</v>
       </c>
       <c r="F12" s="3">
-        <v>148000</v>
+        <v>73500</v>
       </c>
       <c r="G12" s="3">
-        <v>76200</v>
+        <v>147000</v>
       </c>
       <c r="H12" s="3">
-        <v>77300</v>
+        <v>75600</v>
       </c>
       <c r="I12" s="3">
-        <v>71800</v>
+        <v>76700</v>
       </c>
       <c r="J12" s="3">
+        <v>71300</v>
+      </c>
+      <c r="K12" s="3">
         <v>144700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>71600</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -967,8 +981,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1020,38 +1037,41 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>76200</v>
+        <v>3200</v>
       </c>
       <c r="E14" s="3">
-        <v>34800</v>
+        <v>75600</v>
       </c>
       <c r="F14" s="3">
-        <v>93600</v>
+        <v>34600</v>
       </c>
       <c r="G14" s="3">
+        <v>42100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>76700</v>
+      </c>
+      <c r="J14" s="3">
         <v>7600</v>
       </c>
-      <c r="H14" s="3">
-        <v>50100</v>
-      </c>
-      <c r="I14" s="3">
-        <v>16300</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>101200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1073,8 +1093,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1108,8 +1131,8 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1126,8 +1149,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1144,38 +1170,39 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2328500</v>
+        <v>2384000</v>
       </c>
       <c r="E17" s="3">
-        <v>2332900</v>
+        <v>2312700</v>
       </c>
       <c r="F17" s="3">
-        <v>4949800</v>
+        <v>2317000</v>
       </c>
       <c r="G17" s="3">
-        <v>2533100</v>
+        <v>4916100</v>
       </c>
       <c r="H17" s="3">
-        <v>2708300</v>
+        <v>2515900</v>
       </c>
       <c r="I17" s="3">
-        <v>2884600</v>
+        <v>2689900</v>
       </c>
       <c r="J17" s="3">
+        <v>2864900</v>
+      </c>
+      <c r="K17" s="3">
         <v>5574300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2661500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1197,38 +1224,41 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>89200</v>
+        <v>145900</v>
       </c>
       <c r="E18" s="3">
-        <v>198000</v>
+        <v>88600</v>
       </c>
       <c r="F18" s="3">
-        <v>453700</v>
+        <v>196700</v>
       </c>
       <c r="G18" s="3">
-        <v>213300</v>
+        <v>450700</v>
       </c>
       <c r="H18" s="3">
-        <v>19600</v>
+        <v>211800</v>
       </c>
       <c r="I18" s="3">
-        <v>349300</v>
+        <v>19500</v>
       </c>
       <c r="J18" s="3">
+        <v>346900</v>
+      </c>
+      <c r="K18" s="3">
         <v>1031500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>470900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1250,8 +1280,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1271,38 +1304,39 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-30500</v>
+        <v>-20500</v>
       </c>
       <c r="E20" s="3">
-        <v>-12000</v>
+        <v>-30300</v>
       </c>
       <c r="F20" s="3">
-        <v>-43500</v>
+        <v>-11900</v>
       </c>
       <c r="G20" s="3">
-        <v>-23900</v>
+        <v>-43200</v>
       </c>
       <c r="H20" s="3">
-        <v>-34800</v>
+        <v>-23800</v>
       </c>
       <c r="I20" s="3">
-        <v>-21800</v>
+        <v>-34600</v>
       </c>
       <c r="J20" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-16300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1324,28 +1358,31 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>282900</v>
+        <v>329600</v>
       </c>
       <c r="E21" s="3">
-        <v>379700</v>
+        <v>281000</v>
       </c>
       <c r="F21" s="3">
-        <v>773600</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3">
-        <v>754100</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>377200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>768400</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
+        <v>748900</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1377,8 +1414,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1412,8 +1452,8 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1430,38 +1470,41 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>58800</v>
+        <v>125400</v>
       </c>
       <c r="E23" s="3">
-        <v>186100</v>
+        <v>58400</v>
       </c>
       <c r="F23" s="3">
-        <v>410200</v>
+        <v>184800</v>
       </c>
       <c r="G23" s="3">
-        <v>189300</v>
+        <v>407400</v>
       </c>
       <c r="H23" s="3">
-        <v>-15200</v>
+        <v>188000</v>
       </c>
       <c r="I23" s="3">
-        <v>327500</v>
+        <v>-15100</v>
       </c>
       <c r="J23" s="3">
+        <v>325300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1015200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>461100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,38 +1526,41 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>33700</v>
+        <v>38900</v>
       </c>
       <c r="E24" s="3">
-        <v>58800</v>
+        <v>33500</v>
       </c>
       <c r="F24" s="3">
-        <v>100100</v>
+        <v>58400</v>
       </c>
       <c r="G24" s="3">
-        <v>44600</v>
+        <v>99400</v>
       </c>
       <c r="H24" s="3">
-        <v>-25000</v>
+        <v>44300</v>
       </c>
       <c r="I24" s="3">
-        <v>82700</v>
+        <v>-24900</v>
       </c>
       <c r="J24" s="3">
+        <v>82100</v>
+      </c>
+      <c r="K24" s="3">
         <v>218700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>103100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1536,8 +1582,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1589,38 +1638,41 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>25000</v>
+        <v>86500</v>
       </c>
       <c r="E26" s="3">
-        <v>127300</v>
+        <v>24900</v>
       </c>
       <c r="F26" s="3">
-        <v>310100</v>
+        <v>126400</v>
       </c>
       <c r="G26" s="3">
-        <v>144700</v>
+        <v>308000</v>
       </c>
       <c r="H26" s="3">
-        <v>9800</v>
+        <v>143700</v>
       </c>
       <c r="I26" s="3">
-        <v>244800</v>
+        <v>9700</v>
       </c>
       <c r="J26" s="3">
+        <v>243200</v>
+      </c>
+      <c r="K26" s="3">
         <v>796500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>358100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1642,38 +1694,41 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4400</v>
+        <v>85400</v>
       </c>
       <c r="E27" s="3">
-        <v>124000</v>
+        <v>4300</v>
       </c>
       <c r="F27" s="3">
-        <v>303600</v>
+        <v>123200</v>
       </c>
       <c r="G27" s="3">
-        <v>143600</v>
+        <v>301500</v>
       </c>
       <c r="H27" s="3">
+        <v>142700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5400</v>
       </c>
-      <c r="I27" s="3">
-        <v>243700</v>
-      </c>
       <c r="J27" s="3">
+        <v>242100</v>
+      </c>
+      <c r="K27" s="3">
         <v>788900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>357000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,8 +1750,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1748,8 +1806,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1783,8 +1844,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
@@ -1801,8 +1862,11 @@
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1854,8 +1918,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1907,38 +1974,41 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>30500</v>
+        <v>20500</v>
       </c>
       <c r="E32" s="3">
-        <v>12000</v>
+        <v>30300</v>
       </c>
       <c r="F32" s="3">
-        <v>43500</v>
+        <v>11900</v>
       </c>
       <c r="G32" s="3">
-        <v>23900</v>
+        <v>43200</v>
       </c>
       <c r="H32" s="3">
-        <v>34800</v>
+        <v>23800</v>
       </c>
       <c r="I32" s="3">
-        <v>21800</v>
+        <v>34600</v>
       </c>
       <c r="J32" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K32" s="3">
         <v>16300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1960,38 +2030,41 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4400</v>
+        <v>85400</v>
       </c>
       <c r="E33" s="3">
-        <v>124000</v>
+        <v>4300</v>
       </c>
       <c r="F33" s="3">
-        <v>303600</v>
+        <v>123200</v>
       </c>
       <c r="G33" s="3">
-        <v>143600</v>
+        <v>301500</v>
       </c>
       <c r="H33" s="3">
+        <v>142700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5400</v>
       </c>
-      <c r="I33" s="3">
-        <v>243700</v>
-      </c>
       <c r="J33" s="3">
+        <v>242100</v>
+      </c>
+      <c r="K33" s="3">
         <v>788900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>357000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2013,8 +2086,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2066,38 +2142,41 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4400</v>
+        <v>85400</v>
       </c>
       <c r="E35" s="3">
-        <v>124000</v>
+        <v>4300</v>
       </c>
       <c r="F35" s="3">
-        <v>303600</v>
+        <v>123200</v>
       </c>
       <c r="G35" s="3">
-        <v>143600</v>
+        <v>301500</v>
       </c>
       <c r="H35" s="3">
+        <v>142700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5400</v>
       </c>
-      <c r="I35" s="3">
-        <v>243700</v>
-      </c>
       <c r="J35" s="3">
+        <v>242100</v>
+      </c>
+      <c r="K35" s="3">
         <v>788900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>357000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2119,43 +2198,46 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2177,8 +2259,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2198,8 +2283,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2219,22 +2305,23 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2225200</v>
+        <v>2502900</v>
       </c>
       <c r="E41" s="3">
-        <v>2067400</v>
+        <v>2210000</v>
       </c>
       <c r="F41" s="3">
-        <v>1812800</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+        <v>2053300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1800400</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -2251,11 +2338,11 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
@@ -2272,22 +2359,25 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>34800</v>
+        <v>10800</v>
       </c>
       <c r="E42" s="3">
-        <v>14100</v>
+        <v>34600</v>
       </c>
       <c r="F42" s="3">
-        <v>46800</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+        <v>14000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>46500</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -2304,11 +2394,11 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
@@ -2325,22 +2415,25 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1711600</v>
+        <v>1923600</v>
       </c>
       <c r="E43" s="3">
-        <v>1846500</v>
+        <v>1699900</v>
       </c>
       <c r="F43" s="3">
-        <v>1947700</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>1833900</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1934500</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2357,11 +2450,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2378,22 +2471,25 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1314400</v>
+        <v>1433000</v>
       </c>
       <c r="E44" s="3">
-        <v>1465700</v>
+        <v>1305500</v>
       </c>
       <c r="F44" s="3">
-        <v>1500500</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+        <v>1455700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1490300</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -2410,11 +2506,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
@@ -2431,8 +2527,11 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2466,8 +2565,8 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2484,22 +2583,25 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5286000</v>
+        <v>5870400</v>
       </c>
       <c r="E46" s="3">
-        <v>5393700</v>
+        <v>5250000</v>
       </c>
       <c r="F46" s="3">
-        <v>5307800</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+        <v>5357000</v>
+      </c>
+      <c r="G46" s="3">
+        <v>5271700</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -2516,11 +2618,11 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
@@ -2537,22 +2639,25 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>70700</v>
+        <v>70200</v>
       </c>
       <c r="E47" s="3">
-        <v>74000</v>
+        <v>70200</v>
       </c>
       <c r="F47" s="3">
-        <v>76200</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+        <v>73500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>75600</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2569,11 +2674,11 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2590,22 +2695,25 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4058600</v>
+        <v>4048300</v>
       </c>
       <c r="E48" s="3">
-        <v>3736500</v>
+        <v>4031000</v>
       </c>
       <c r="F48" s="3">
-        <v>3660400</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+        <v>3711100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>3635500</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -2622,11 +2730,11 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2643,22 +2751,25 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5936700</v>
+        <v>5907100</v>
       </c>
       <c r="E49" s="3">
-        <v>5231600</v>
+        <v>5896300</v>
       </c>
       <c r="F49" s="3">
-        <v>5206600</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
+        <v>5196000</v>
+      </c>
+      <c r="G49" s="3">
+        <v>5171100</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -2675,11 +2786,11 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2696,8 +2807,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2749,8 +2863,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2802,22 +2919,25 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>443900</v>
+        <v>440900</v>
       </c>
       <c r="E52" s="3">
-        <v>435200</v>
+        <v>440900</v>
       </c>
       <c r="F52" s="3">
-        <v>455900</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+        <v>432300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>452800</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2834,11 +2954,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2855,8 +2975,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2908,22 +3031,25 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>15795900</v>
+        <v>16336900</v>
       </c>
       <c r="E54" s="3">
-        <v>14871100</v>
+        <v>15688500</v>
       </c>
       <c r="F54" s="3">
-        <v>14706800</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+        <v>14769900</v>
+      </c>
+      <c r="G54" s="3">
+        <v>14606700</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2940,11 +3066,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
+        <v>0</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
@@ -2961,8 +3087,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2982,8 +3111,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3003,22 +3133,23 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1127300</v>
+        <v>1154200</v>
       </c>
       <c r="E57" s="3">
-        <v>1029300</v>
+        <v>1119600</v>
       </c>
       <c r="F57" s="3">
-        <v>1085900</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>1022300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1078500</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -3035,11 +3166,11 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -3056,22 +3187,25 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>588700</v>
+        <v>1347600</v>
       </c>
       <c r="E58" s="3">
-        <v>722500</v>
+        <v>584700</v>
       </c>
       <c r="F58" s="3">
-        <v>718100</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>717600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>713300</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -3088,11 +3222,11 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3109,22 +3243,25 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>546200</v>
+        <v>583600</v>
       </c>
       <c r="E59" s="3">
-        <v>646300</v>
+        <v>542500</v>
       </c>
       <c r="F59" s="3">
-        <v>613700</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+        <v>641900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>609500</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -3141,11 +3278,11 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -3162,22 +3299,25 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2262200</v>
+        <v>3085400</v>
       </c>
       <c r="E60" s="3">
-        <v>2398200</v>
+        <v>2246800</v>
       </c>
       <c r="F60" s="3">
-        <v>2417800</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>2381900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2401300</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -3194,11 +3334,11 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
@@ -3215,22 +3355,25 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4063000</v>
+        <v>3276700</v>
       </c>
       <c r="E61" s="3">
-        <v>3215300</v>
+        <v>4035300</v>
       </c>
       <c r="F61" s="3">
-        <v>3211000</v>
+        <v>3193500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3189100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -3268,22 +3411,25 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1359000</v>
+        <v>1344400</v>
       </c>
       <c r="E62" s="3">
-        <v>1215400</v>
+        <v>1349800</v>
       </c>
       <c r="F62" s="3">
-        <v>1275300</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+        <v>1207100</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1266600</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -3300,11 +3446,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3321,8 +3467,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3374,8 +3523,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3427,8 +3579,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3480,22 +3635,25 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7958400</v>
+        <v>7973400</v>
       </c>
       <c r="E66" s="3">
-        <v>6873500</v>
+        <v>7904200</v>
       </c>
       <c r="F66" s="3">
-        <v>6946400</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+        <v>6826800</v>
+      </c>
+      <c r="G66" s="3">
+        <v>6899200</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -3512,11 +3670,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
+        <v>0</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
@@ -3533,8 +3691,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3554,8 +3715,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3607,8 +3769,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3660,8 +3825,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3695,8 +3863,8 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
+      <c r="N70" s="3">
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>3</v>
@@ -3713,8 +3881,11 @@
       <c r="S70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3766,22 +3937,25 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4936700</v>
+        <v>4986300</v>
       </c>
       <c r="E72" s="3">
-        <v>4967200</v>
+        <v>4903100</v>
       </c>
       <c r="F72" s="3">
-        <v>4838800</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+        <v>4933400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>4805900</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -3798,11 +3972,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
@@ -3819,8 +3993,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3872,8 +4049,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3925,8 +4105,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3978,22 +4161,25 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7837600</v>
+        <v>8363500</v>
       </c>
       <c r="E76" s="3">
-        <v>7997500</v>
+        <v>7784300</v>
       </c>
       <c r="F76" s="3">
-        <v>7760300</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+        <v>7943100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>7707600</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -4010,11 +4196,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -4031,8 +4217,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4084,43 +4273,46 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4142,38 +4334,41 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4400</v>
+        <v>85400</v>
       </c>
       <c r="E81" s="3">
-        <v>124000</v>
+        <v>4300</v>
       </c>
       <c r="F81" s="3">
-        <v>303600</v>
+        <v>123200</v>
       </c>
       <c r="G81" s="3">
-        <v>143600</v>
+        <v>301500</v>
       </c>
       <c r="H81" s="3">
+        <v>142700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5400</v>
       </c>
-      <c r="I81" s="3">
-        <v>243700</v>
-      </c>
       <c r="J81" s="3">
+        <v>242100</v>
+      </c>
+      <c r="K81" s="3">
         <v>788900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>357000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4195,8 +4390,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4216,22 +4414,23 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>224100</v>
+        <v>204300</v>
       </c>
       <c r="E83" s="3">
-        <v>193700</v>
+        <v>222600</v>
       </c>
       <c r="F83" s="3">
-        <v>363400</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>192400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>361000</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -4245,14 +4444,14 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4269,8 +4468,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4322,8 +4524,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4375,8 +4580,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4428,8 +4636,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4481,8 +4692,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4534,22 +4748,25 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>502700</v>
+        <v>91900</v>
       </c>
       <c r="E89" s="3">
-        <v>427600</v>
+        <v>499300</v>
       </c>
       <c r="F89" s="3">
-        <v>453700</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>424700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>450700</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -4563,14 +4780,14 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4587,8 +4804,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4608,20 +4828,21 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-170000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-181000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-149000</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -4643,8 +4864,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -4661,8 +4882,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4714,8 +4938,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4767,22 +4994,25 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-917300</v>
+        <v>-203200</v>
       </c>
       <c r="E94" s="3">
-        <v>-136000</v>
+        <v>-911000</v>
       </c>
       <c r="F94" s="3">
-        <v>-421100</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-135100</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-418200</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -4796,14 +5026,14 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4820,8 +5050,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4841,8 +5074,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4853,10 +5087,10 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-275300</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-273400</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -4894,8 +5128,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4947,8 +5184,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5000,8 +5240,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5053,22 +5296,25 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>562500</v>
+        <v>397700</v>
       </c>
       <c r="E100" s="3">
-        <v>-41300</v>
+        <v>558700</v>
       </c>
       <c r="F100" s="3">
-        <v>40300</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>-41100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>40000</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -5082,14 +5328,14 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -5106,23 +5352,26 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>9800</v>
+        <v>6500</v>
       </c>
       <c r="E101" s="3">
-        <v>4400</v>
+        <v>9700</v>
       </c>
       <c r="F101" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G101" s="3">
         <v>7600</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5135,14 +5384,14 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -5159,22 +5408,25 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>157800</v>
+        <v>292900</v>
       </c>
       <c r="E102" s="3">
-        <v>254600</v>
+        <v>156700</v>
       </c>
       <c r="F102" s="3">
-        <v>80500</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>252900</v>
+      </c>
+      <c r="G102" s="3">
+        <v>80000</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -5188,14 +5440,14 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -5210,6 +5462,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,41 +739,44 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2529900</v>
+        <v>2808900</v>
       </c>
       <c r="E8" s="3">
-        <v>2401300</v>
+        <v>2592900</v>
       </c>
       <c r="F8" s="3">
-        <v>2513700</v>
+        <v>2461100</v>
       </c>
       <c r="G8" s="3">
-        <v>5366800</v>
+        <v>2576300</v>
       </c>
       <c r="H8" s="3">
-        <v>2727700</v>
+        <v>5500300</v>
       </c>
       <c r="I8" s="3">
-        <v>2709300</v>
+        <v>2795600</v>
       </c>
       <c r="J8" s="3">
+        <v>2776800</v>
+      </c>
+      <c r="K8" s="3">
         <v>3211800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6605900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3132400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -794,41 +798,44 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2024200</v>
+        <v>2176400</v>
       </c>
       <c r="E9" s="3">
-        <v>1942000</v>
+        <v>2074500</v>
       </c>
       <c r="F9" s="3">
-        <v>1983100</v>
+        <v>1990400</v>
       </c>
       <c r="G9" s="3">
-        <v>4238500</v>
+        <v>2032400</v>
       </c>
       <c r="H9" s="3">
-        <v>2185200</v>
+        <v>4344000</v>
       </c>
       <c r="I9" s="3">
-        <v>2300800</v>
+        <v>2239600</v>
       </c>
       <c r="J9" s="3">
+        <v>2358100</v>
+      </c>
+      <c r="K9" s="3">
         <v>2546100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4880100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2316500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,41 +857,44 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>505800</v>
+        <v>632400</v>
       </c>
       <c r="E10" s="3">
-        <v>459300</v>
+        <v>518400</v>
       </c>
       <c r="F10" s="3">
-        <v>530600</v>
+        <v>470700</v>
       </c>
       <c r="G10" s="3">
-        <v>1128300</v>
+        <v>543800</v>
       </c>
       <c r="H10" s="3">
-        <v>542500</v>
+        <v>1156300</v>
       </c>
       <c r="I10" s="3">
-        <v>408500</v>
+        <v>556000</v>
       </c>
       <c r="J10" s="3">
+        <v>418700</v>
+      </c>
+      <c r="K10" s="3">
         <v>665700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1725700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>815900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -906,8 +916,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -928,41 +941,42 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>74600</v>
+        <v>75300</v>
       </c>
       <c r="E12" s="3">
-        <v>76700</v>
+        <v>76400</v>
       </c>
       <c r="F12" s="3">
-        <v>73500</v>
+        <v>78600</v>
       </c>
       <c r="G12" s="3">
-        <v>147000</v>
+        <v>75300</v>
       </c>
       <c r="H12" s="3">
-        <v>75600</v>
+        <v>150600</v>
       </c>
       <c r="I12" s="3">
-        <v>76700</v>
+        <v>77500</v>
       </c>
       <c r="J12" s="3">
+        <v>78600</v>
+      </c>
+      <c r="K12" s="3">
         <v>71300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>144700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>71600</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +998,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1040,41 +1057,44 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3200</v>
+        <v>42100</v>
       </c>
       <c r="E14" s="3">
-        <v>75600</v>
+        <v>3300</v>
       </c>
       <c r="F14" s="3">
-        <v>34600</v>
+        <v>77500</v>
       </c>
       <c r="G14" s="3">
-        <v>42100</v>
+        <v>35400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="I14" s="3">
-        <v>76700</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>78600</v>
+      </c>
+      <c r="K14" s="3">
         <v>7600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>101200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1096,8 +1116,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1134,8 +1157,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1152,8 +1175,11 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1171,41 +1197,42 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2384000</v>
+        <v>2568500</v>
       </c>
       <c r="E17" s="3">
-        <v>2312700</v>
+        <v>2443400</v>
       </c>
       <c r="F17" s="3">
-        <v>2317000</v>
+        <v>2370300</v>
       </c>
       <c r="G17" s="3">
-        <v>4916100</v>
+        <v>2374700</v>
       </c>
       <c r="H17" s="3">
-        <v>2515900</v>
+        <v>5038500</v>
       </c>
       <c r="I17" s="3">
-        <v>2689900</v>
+        <v>2578500</v>
       </c>
       <c r="J17" s="3">
+        <v>2756800</v>
+      </c>
+      <c r="K17" s="3">
         <v>2864900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5574300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2661500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,41 +1254,44 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>145900</v>
+        <v>240300</v>
       </c>
       <c r="E18" s="3">
-        <v>88600</v>
+        <v>149500</v>
       </c>
       <c r="F18" s="3">
-        <v>196700</v>
+        <v>90800</v>
       </c>
       <c r="G18" s="3">
-        <v>450700</v>
+        <v>201600</v>
       </c>
       <c r="H18" s="3">
-        <v>211800</v>
+        <v>461900</v>
       </c>
       <c r="I18" s="3">
-        <v>19500</v>
+        <v>217100</v>
       </c>
       <c r="J18" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K18" s="3">
         <v>346900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1031500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>470900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,8 +1313,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1305,41 +1338,42 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-20500</v>
+        <v>-17700</v>
       </c>
       <c r="E20" s="3">
-        <v>-30300</v>
+        <v>-21000</v>
       </c>
       <c r="F20" s="3">
-        <v>-11900</v>
+        <v>-31000</v>
       </c>
       <c r="G20" s="3">
-        <v>-43200</v>
+        <v>-12200</v>
       </c>
       <c r="H20" s="3">
-        <v>-23800</v>
+        <v>-44300</v>
       </c>
       <c r="I20" s="3">
-        <v>-34600</v>
+        <v>-24400</v>
       </c>
       <c r="J20" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-21600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1361,31 +1395,34 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>329600</v>
+        <v>436400</v>
       </c>
       <c r="E21" s="3">
-        <v>281000</v>
+        <v>337800</v>
       </c>
       <c r="F21" s="3">
-        <v>377200</v>
+        <v>288000</v>
       </c>
       <c r="G21" s="3">
-        <v>768400</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3">
-        <v>748900</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>386600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>787500</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
+        <v>767600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1417,8 +1454,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1455,8 +1495,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1473,41 +1513,44 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>125400</v>
+        <v>222600</v>
       </c>
       <c r="E23" s="3">
-        <v>58400</v>
+        <v>128500</v>
       </c>
       <c r="F23" s="3">
-        <v>184800</v>
+        <v>59800</v>
       </c>
       <c r="G23" s="3">
-        <v>407400</v>
+        <v>189400</v>
       </c>
       <c r="H23" s="3">
-        <v>188000</v>
+        <v>417600</v>
       </c>
       <c r="I23" s="3">
-        <v>-15100</v>
+        <v>192700</v>
       </c>
       <c r="J23" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K23" s="3">
         <v>325300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1015200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>461100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1529,41 +1572,44 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>38900</v>
+        <v>57600</v>
       </c>
       <c r="E24" s="3">
-        <v>33500</v>
+        <v>39900</v>
       </c>
       <c r="F24" s="3">
-        <v>58400</v>
+        <v>34300</v>
       </c>
       <c r="G24" s="3">
-        <v>99400</v>
+        <v>59800</v>
       </c>
       <c r="H24" s="3">
-        <v>44300</v>
+        <v>101900</v>
       </c>
       <c r="I24" s="3">
-        <v>-24900</v>
+        <v>45400</v>
       </c>
       <c r="J24" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="K24" s="3">
         <v>82100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>218700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>103100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,8 +1631,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1641,41 +1690,44 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>86500</v>
+        <v>165000</v>
       </c>
       <c r="E26" s="3">
-        <v>24900</v>
+        <v>88600</v>
       </c>
       <c r="F26" s="3">
-        <v>126400</v>
+        <v>25500</v>
       </c>
       <c r="G26" s="3">
-        <v>308000</v>
+        <v>129600</v>
       </c>
       <c r="H26" s="3">
-        <v>143700</v>
+        <v>315700</v>
       </c>
       <c r="I26" s="3">
-        <v>9700</v>
+        <v>147300</v>
       </c>
       <c r="J26" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K26" s="3">
         <v>243200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>796500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>358100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,41 +1749,44 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>85400</v>
+        <v>160600</v>
       </c>
       <c r="E27" s="3">
-        <v>4300</v>
+        <v>87500</v>
       </c>
       <c r="F27" s="3">
-        <v>123200</v>
+        <v>4400</v>
       </c>
       <c r="G27" s="3">
-        <v>301500</v>
+        <v>126300</v>
       </c>
       <c r="H27" s="3">
-        <v>142700</v>
+        <v>309000</v>
       </c>
       <c r="I27" s="3">
-        <v>-5400</v>
+        <v>146200</v>
       </c>
       <c r="J27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K27" s="3">
         <v>242100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>788900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>357000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1753,8 +1808,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1809,8 +1867,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1847,8 +1908,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
@@ -1865,8 +1926,11 @@
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1921,8 +1985,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1977,41 +2044,44 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>20500</v>
+        <v>17700</v>
       </c>
       <c r="E32" s="3">
-        <v>30300</v>
+        <v>21000</v>
       </c>
       <c r="F32" s="3">
-        <v>11900</v>
+        <v>31000</v>
       </c>
       <c r="G32" s="3">
-        <v>43200</v>
+        <v>12200</v>
       </c>
       <c r="H32" s="3">
-        <v>23800</v>
+        <v>44300</v>
       </c>
       <c r="I32" s="3">
-        <v>34600</v>
+        <v>24400</v>
       </c>
       <c r="J32" s="3">
+        <v>35400</v>
+      </c>
+      <c r="K32" s="3">
         <v>21600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,41 +2103,44 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>85400</v>
+        <v>160600</v>
       </c>
       <c r="E33" s="3">
-        <v>4300</v>
+        <v>87500</v>
       </c>
       <c r="F33" s="3">
-        <v>123200</v>
+        <v>4400</v>
       </c>
       <c r="G33" s="3">
-        <v>301500</v>
+        <v>126300</v>
       </c>
       <c r="H33" s="3">
-        <v>142700</v>
+        <v>309000</v>
       </c>
       <c r="I33" s="3">
-        <v>-5400</v>
+        <v>146200</v>
       </c>
       <c r="J33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K33" s="3">
         <v>242100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>788900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>357000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2089,8 +2162,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2145,41 +2221,44 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>85400</v>
+        <v>160600</v>
       </c>
       <c r="E35" s="3">
-        <v>4300</v>
+        <v>87500</v>
       </c>
       <c r="F35" s="3">
-        <v>123200</v>
+        <v>4400</v>
       </c>
       <c r="G35" s="3">
-        <v>301500</v>
+        <v>126300</v>
       </c>
       <c r="H35" s="3">
-        <v>142700</v>
+        <v>309000</v>
       </c>
       <c r="I35" s="3">
-        <v>-5400</v>
+        <v>146200</v>
       </c>
       <c r="J35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K35" s="3">
         <v>242100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>788900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>357000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2201,46 +2280,49 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2262,8 +2344,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2284,8 +2369,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2306,25 +2392,26 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2502900</v>
+        <v>2319300</v>
       </c>
       <c r="E41" s="3">
-        <v>2210000</v>
+        <v>2565200</v>
       </c>
       <c r="F41" s="3">
-        <v>2053300</v>
+        <v>2265000</v>
       </c>
       <c r="G41" s="3">
-        <v>1800400</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+        <v>2104400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1845300</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -2341,11 +2428,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
@@ -2362,25 +2449,28 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10800</v>
+        <v>13300</v>
       </c>
       <c r="E42" s="3">
-        <v>34600</v>
+        <v>11100</v>
       </c>
       <c r="F42" s="3">
-        <v>14000</v>
+        <v>35400</v>
       </c>
       <c r="G42" s="3">
-        <v>46500</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+        <v>14400</v>
+      </c>
+      <c r="H42" s="3">
+        <v>47600</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -2397,11 +2487,11 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2418,25 +2508,28 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1923600</v>
+        <v>2065700</v>
       </c>
       <c r="E43" s="3">
-        <v>1699900</v>
+        <v>1971500</v>
       </c>
       <c r="F43" s="3">
-        <v>1833900</v>
+        <v>1742300</v>
       </c>
       <c r="G43" s="3">
-        <v>1934500</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+        <v>1879600</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1982600</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -2453,11 +2546,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2474,25 +2567,28 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1433000</v>
+        <v>1507400</v>
       </c>
       <c r="E44" s="3">
-        <v>1305500</v>
+        <v>1468700</v>
       </c>
       <c r="F44" s="3">
-        <v>1455700</v>
+        <v>1338000</v>
       </c>
       <c r="G44" s="3">
-        <v>1490300</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+        <v>1491900</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1527400</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -2509,11 +2605,11 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
@@ -2530,8 +2626,11 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2568,8 +2667,8 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2586,25 +2685,28 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5870400</v>
+        <v>5905700</v>
       </c>
       <c r="E46" s="3">
-        <v>5250000</v>
+        <v>6016500</v>
       </c>
       <c r="F46" s="3">
-        <v>5357000</v>
+        <v>5380700</v>
       </c>
       <c r="G46" s="3">
-        <v>5271700</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+        <v>5490400</v>
+      </c>
+      <c r="H46" s="3">
+        <v>5402900</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -2621,11 +2723,11 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
@@ -2642,25 +2744,28 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>70200</v>
+        <v>73100</v>
       </c>
       <c r="E47" s="3">
-        <v>70200</v>
+        <v>72000</v>
       </c>
       <c r="F47" s="3">
-        <v>73500</v>
+        <v>72000</v>
       </c>
       <c r="G47" s="3">
-        <v>75600</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+        <v>75300</v>
+      </c>
+      <c r="H47" s="3">
+        <v>77500</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -2677,11 +2782,11 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2698,25 +2803,28 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4048300</v>
+        <v>4194500</v>
       </c>
       <c r="E48" s="3">
-        <v>4031000</v>
+        <v>4149100</v>
       </c>
       <c r="F48" s="3">
-        <v>3711100</v>
+        <v>4131300</v>
       </c>
       <c r="G48" s="3">
-        <v>3635500</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+        <v>3803500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>3726000</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -2733,11 +2841,11 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2754,25 +2862,28 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5907100</v>
+        <v>6048600</v>
       </c>
       <c r="E49" s="3">
-        <v>5896300</v>
+        <v>6054100</v>
       </c>
       <c r="F49" s="3">
-        <v>5196000</v>
+        <v>6043100</v>
       </c>
       <c r="G49" s="3">
-        <v>5171100</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+        <v>5325300</v>
+      </c>
+      <c r="H49" s="3">
+        <v>5299900</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -2789,11 +2900,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2810,8 +2921,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2866,8 +2980,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2922,25 +3039,28 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>440900</v>
+        <v>492900</v>
       </c>
       <c r="E52" s="3">
-        <v>440900</v>
+        <v>451900</v>
       </c>
       <c r="F52" s="3">
-        <v>432300</v>
+        <v>451900</v>
       </c>
       <c r="G52" s="3">
-        <v>452800</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+        <v>443000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>464100</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2957,11 +3077,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -2978,8 +3098,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3034,25 +3157,28 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16336900</v>
+        <v>16714800</v>
       </c>
       <c r="E54" s="3">
-        <v>15688500</v>
+        <v>16743600</v>
       </c>
       <c r="F54" s="3">
-        <v>14769900</v>
+        <v>16079000</v>
       </c>
       <c r="G54" s="3">
-        <v>14606700</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+        <v>15137600</v>
+      </c>
+      <c r="H54" s="3">
+        <v>14970300</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -3069,11 +3195,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3">
-        <v>0</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
+        <v>0</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
@@ -3090,8 +3216,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3112,8 +3241,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3134,25 +3264,26 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1154200</v>
+        <v>1233900</v>
       </c>
       <c r="E57" s="3">
-        <v>1119600</v>
+        <v>1182900</v>
       </c>
       <c r="F57" s="3">
-        <v>1022300</v>
+        <v>1147500</v>
       </c>
       <c r="G57" s="3">
-        <v>1078500</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+        <v>1047800</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1105400</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -3169,11 +3300,11 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -3190,25 +3321,28 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1347600</v>
+        <v>1357900</v>
       </c>
       <c r="E58" s="3">
-        <v>584700</v>
+        <v>1381200</v>
       </c>
       <c r="F58" s="3">
-        <v>717600</v>
+        <v>599200</v>
       </c>
       <c r="G58" s="3">
-        <v>713300</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>735400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>731000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -3225,11 +3359,11 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3246,25 +3380,28 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>583600</v>
+        <v>588100</v>
       </c>
       <c r="E59" s="3">
-        <v>542500</v>
+        <v>598100</v>
       </c>
       <c r="F59" s="3">
-        <v>641900</v>
+        <v>556000</v>
       </c>
       <c r="G59" s="3">
-        <v>609500</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+        <v>657900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>624700</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -3281,11 +3418,11 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
@@ -3302,25 +3439,28 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3085400</v>
+        <v>3179900</v>
       </c>
       <c r="E60" s="3">
-        <v>2246800</v>
+        <v>3162200</v>
       </c>
       <c r="F60" s="3">
-        <v>2381900</v>
+        <v>2302700</v>
       </c>
       <c r="G60" s="3">
-        <v>2401300</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+        <v>2441200</v>
+      </c>
+      <c r="H60" s="3">
+        <v>2461100</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -3337,11 +3477,11 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
+        <v>0</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
@@ -3358,25 +3498,28 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3276700</v>
+        <v>3364900</v>
       </c>
       <c r="E61" s="3">
-        <v>4035300</v>
+        <v>3358200</v>
       </c>
       <c r="F61" s="3">
-        <v>3193500</v>
+        <v>4135800</v>
       </c>
       <c r="G61" s="3">
-        <v>3189100</v>
+        <v>3273000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>3268500</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -3414,25 +3557,28 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1344400</v>
+        <v>1415500</v>
       </c>
       <c r="E62" s="3">
-        <v>1349800</v>
+        <v>1377900</v>
       </c>
       <c r="F62" s="3">
-        <v>1207100</v>
+        <v>1383400</v>
       </c>
       <c r="G62" s="3">
-        <v>1266600</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>1237200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1298100</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -3449,11 +3595,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3470,8 +3616,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3526,8 +3675,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3582,8 +3734,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3638,25 +3793,28 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7973400</v>
+        <v>8232800</v>
       </c>
       <c r="E66" s="3">
-        <v>7904200</v>
+        <v>8171900</v>
       </c>
       <c r="F66" s="3">
-        <v>6826800</v>
+        <v>8101000</v>
       </c>
       <c r="G66" s="3">
-        <v>6899200</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+        <v>6996700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>7070900</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -3673,11 +3831,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
+        <v>0</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
@@ -3694,8 +3852,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3716,8 +3877,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3772,8 +3934,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3828,8 +3993,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3866,8 +4034,8 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3" t="s">
-        <v>3</v>
+      <c r="O70" s="3">
+        <v>0</v>
       </c>
       <c r="P70" s="3" t="s">
         <v>3</v>
@@ -3884,8 +4052,11 @@
       <c r="T70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3940,25 +4111,28 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4986300</v>
+        <v>5009700</v>
       </c>
       <c r="E72" s="3">
-        <v>4903100</v>
+        <v>5110500</v>
       </c>
       <c r="F72" s="3">
-        <v>4933400</v>
+        <v>5025200</v>
       </c>
       <c r="G72" s="3">
-        <v>4805900</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+        <v>5056200</v>
+      </c>
+      <c r="H72" s="3">
+        <v>4925500</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -3975,11 +4149,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3996,8 +4170,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4052,8 +4229,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4108,8 +4288,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4164,25 +4347,28 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8363500</v>
+        <v>8482000</v>
       </c>
       <c r="E76" s="3">
-        <v>7784300</v>
+        <v>8571700</v>
       </c>
       <c r="F76" s="3">
-        <v>7943100</v>
+        <v>7978000</v>
       </c>
       <c r="G76" s="3">
-        <v>7707600</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+        <v>8140900</v>
+      </c>
+      <c r="H76" s="3">
+        <v>7899400</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -4199,11 +4385,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3">
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -4220,8 +4406,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4276,46 +4465,49 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4337,41 +4529,44 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>85400</v>
+        <v>160600</v>
       </c>
       <c r="E81" s="3">
-        <v>4300</v>
+        <v>87500</v>
       </c>
       <c r="F81" s="3">
-        <v>123200</v>
+        <v>4400</v>
       </c>
       <c r="G81" s="3">
-        <v>301500</v>
+        <v>126300</v>
       </c>
       <c r="H81" s="3">
-        <v>142700</v>
+        <v>309000</v>
       </c>
       <c r="I81" s="3">
-        <v>-5400</v>
+        <v>146200</v>
       </c>
       <c r="J81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K81" s="3">
         <v>242100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>788900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>357000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4393,8 +4588,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4415,25 +4613,26 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>204300</v>
+        <v>213800</v>
       </c>
       <c r="E83" s="3">
-        <v>222600</v>
+        <v>209300</v>
       </c>
       <c r="F83" s="3">
-        <v>192400</v>
+        <v>228200</v>
       </c>
       <c r="G83" s="3">
-        <v>361000</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>197200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>369900</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -4447,14 +4646,14 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4471,8 +4670,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4527,8 +4729,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4583,8 +4788,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4639,8 +4847,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4695,8 +4906,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4751,25 +4965,28 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>91900</v>
+        <v>326700</v>
       </c>
       <c r="E89" s="3">
-        <v>499300</v>
+        <v>94100</v>
       </c>
       <c r="F89" s="3">
-        <v>424700</v>
+        <v>511700</v>
       </c>
       <c r="G89" s="3">
-        <v>450700</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+        <v>435300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>461900</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -4783,14 +5000,14 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
@@ -4807,8 +5024,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4829,23 +5049,24 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-170000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-181000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-149000</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -4867,8 +5088,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4885,8 +5106,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4941,8 +5165,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4997,25 +5224,28 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-203200</v>
+        <v>-219300</v>
       </c>
       <c r="E94" s="3">
-        <v>-911000</v>
+        <v>-208200</v>
       </c>
       <c r="F94" s="3">
-        <v>-135100</v>
+        <v>-933700</v>
       </c>
       <c r="G94" s="3">
-        <v>-418200</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+        <v>-138500</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-428600</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -5029,14 +5259,14 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -5053,8 +5283,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5075,13 +5308,14 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-289100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -5090,10 +5324,10 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-273400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-280200</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -5131,8 +5365,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5187,8 +5424,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5243,8 +5483,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5299,25 +5542,28 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>397700</v>
+        <v>-345600</v>
       </c>
       <c r="E100" s="3">
-        <v>558700</v>
+        <v>407600</v>
       </c>
       <c r="F100" s="3">
-        <v>-41100</v>
+        <v>572600</v>
       </c>
       <c r="G100" s="3">
-        <v>40000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+        <v>-42100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>41000</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -5331,14 +5577,14 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -5355,25 +5601,28 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6500</v>
+        <v>-7800</v>
       </c>
       <c r="E101" s="3">
-        <v>9700</v>
+        <v>6600</v>
       </c>
       <c r="F101" s="3">
-        <v>4300</v>
+        <v>10000</v>
       </c>
       <c r="G101" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+        <v>4400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>7800</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -5387,14 +5636,14 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5411,25 +5660,28 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>292900</v>
+        <v>-245900</v>
       </c>
       <c r="E102" s="3">
-        <v>156700</v>
+        <v>300200</v>
       </c>
       <c r="F102" s="3">
-        <v>252900</v>
+        <v>160600</v>
       </c>
       <c r="G102" s="3">
-        <v>80000</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+        <v>259200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>82000</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
@@ -5443,14 +5695,14 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
@@ -5465,6 +5717,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -742,44 +743,47 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>2808900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2592900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2461100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2576300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5500300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2795600</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>2776800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3211800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6605900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3132400</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,44 +805,47 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>2176400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2074500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1990400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2032400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4344000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2239600</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>2358100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2546100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4880100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2316500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -860,44 +867,47 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>632400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>518400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>470700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>543800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1156300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>556000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>418700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>665700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1725700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>815900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,8 +929,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -942,44 +955,45 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>75300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>76400</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>78600</v>
       </c>
-      <c r="G12" s="3">
-        <v>75300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>150600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>77500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>78600</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>71300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>144700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>71600</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,8 +1015,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1060,44 +1077,47 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>42100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>77500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>35400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>43200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>78600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>101200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1119,31 +1139,34 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1160,8 +1183,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1178,8 +1201,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1198,44 +1224,45 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>2568500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2443400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2370300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2374700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5038500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2578500</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>2756800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2864900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5574300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2661500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,44 +1284,47 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>240300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>149500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>90800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>201600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>461900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>217100</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>19900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>346900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1031500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>470900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1346,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1339,44 +1372,45 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-44300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-24400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-35400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-16300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1398,35 +1432,38 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>436400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>337800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>288000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>386600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>787500</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>767600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1457,31 +1494,34 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1498,8 +1538,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1516,44 +1556,47 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>222600</v>
-      </c>
-      <c r="E23" s="3">
-        <v>128500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>59800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>189400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>417600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>192700</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>-15500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>325300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1015200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>461100</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,44 +1618,47 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>57600</v>
-      </c>
-      <c r="E24" s="3">
-        <v>39900</v>
-      </c>
-      <c r="F24" s="3">
-        <v>34300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>59800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>101900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>45400</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>-25500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>82100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>218700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>103100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1634,8 +1680,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1693,44 +1742,47 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>165000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>88600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>25500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>129600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>315700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>147300</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>243200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>796500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>358100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1752,44 +1804,47 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>160600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>87500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>126300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>309000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>146200</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>242100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>788900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>357000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1811,8 +1866,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1870,31 +1928,34 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1911,8 +1972,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1990,11 @@
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1988,8 +2052,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2047,44 +2114,47 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>17700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>21000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>31000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>12200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>44300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>24400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>35400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>16300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2106,44 +2176,47 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>160600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>87500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>126300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>309000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>146200</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>242100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>788900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>357000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,8 +2238,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2224,44 +2300,47 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>160600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>87500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>126300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>309000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>146200</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>242100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>788900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>357000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,49 +2362,52 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2347,8 +2429,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2370,8 +2455,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2393,31 +2479,32 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2319300</v>
+        <v>2225100</v>
       </c>
       <c r="E41" s="3">
-        <v>2565200</v>
+        <v>2243700</v>
       </c>
       <c r="F41" s="3">
-        <v>2265000</v>
+        <v>2498700</v>
       </c>
       <c r="G41" s="3">
-        <v>2104400</v>
+        <v>2260400</v>
       </c>
       <c r="H41" s="3">
-        <v>1845300</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>2011000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1818800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2082800</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -2431,11 +2518,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
@@ -2452,31 +2539,34 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>13300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>11100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>35400</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>14400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>47600</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2490,11 +2580,11 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2511,31 +2601,34 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2065700</v>
+        <v>1910600</v>
       </c>
       <c r="E43" s="3">
-        <v>1971500</v>
+        <v>1998300</v>
       </c>
       <c r="F43" s="3">
-        <v>1742300</v>
+        <v>1920400</v>
       </c>
       <c r="G43" s="3">
-        <v>1879600</v>
+        <v>1738700</v>
       </c>
       <c r="H43" s="3">
-        <v>1982600</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>1796100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1954100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2041500</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2549,11 +2642,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -2570,31 +2663,34 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1507400</v>
+        <v>1552500</v>
       </c>
       <c r="E44" s="3">
-        <v>1468700</v>
+        <v>1458300</v>
       </c>
       <c r="F44" s="3">
-        <v>1338000</v>
+        <v>1430600</v>
       </c>
       <c r="G44" s="3">
-        <v>1491900</v>
+        <v>1335200</v>
       </c>
       <c r="H44" s="3">
-        <v>1527400</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>1425700</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1505500</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1597100</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -2608,11 +2704,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
@@ -2629,31 +2725,34 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>35400</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>46900</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2670,8 +2769,8 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2688,31 +2787,34 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5905700</v>
+        <v>5736100</v>
       </c>
       <c r="E46" s="3">
-        <v>6016500</v>
+        <v>5713100</v>
       </c>
       <c r="F46" s="3">
-        <v>5380700</v>
+        <v>5860400</v>
       </c>
       <c r="G46" s="3">
-        <v>5490400</v>
+        <v>5369700</v>
       </c>
       <c r="H46" s="3">
-        <v>5402900</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>5246600</v>
+      </c>
+      <c r="I46" s="3">
+        <v>5325300</v>
+      </c>
+      <c r="J46" s="3">
+        <v>5779000</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2726,11 +2828,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
@@ -2747,31 +2849,34 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>73100</v>
+        <v>74700</v>
       </c>
       <c r="E47" s="3">
+        <v>70700</v>
+      </c>
+      <c r="F47" s="3">
+        <v>70100</v>
+      </c>
+      <c r="G47" s="3">
+        <v>71800</v>
+      </c>
+      <c r="H47" s="3">
         <v>72000</v>
       </c>
-      <c r="F47" s="3">
-        <v>72000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>75300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>77500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="I47" s="3">
+        <v>76400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>79300</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2785,11 +2890,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2806,31 +2911,34 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4194500</v>
+        <v>4165700</v>
       </c>
       <c r="E48" s="3">
-        <v>4149100</v>
+        <v>4057600</v>
       </c>
       <c r="F48" s="3">
-        <v>4131300</v>
+        <v>4041400</v>
       </c>
       <c r="G48" s="3">
-        <v>3803500</v>
+        <v>4122900</v>
       </c>
       <c r="H48" s="3">
-        <v>3726000</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>3634600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3672500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3657100</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2844,11 +2952,11 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2865,31 +2973,34 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6048600</v>
+        <v>5958100</v>
       </c>
       <c r="E49" s="3">
-        <v>6054100</v>
+        <v>5818100</v>
       </c>
       <c r="F49" s="3">
-        <v>6043100</v>
+        <v>5897100</v>
       </c>
       <c r="G49" s="3">
-        <v>5325300</v>
+        <v>5994300</v>
       </c>
       <c r="H49" s="3">
-        <v>5299900</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>5088900</v>
+      </c>
+      <c r="I49" s="3">
+        <v>5186700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>5167300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2903,11 +3014,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2924,8 +3035,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2983,8 +3097,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3042,31 +3159,34 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>492900</v>
+        <v>287800</v>
       </c>
       <c r="E52" s="3">
-        <v>451900</v>
+        <v>315000</v>
       </c>
       <c r="F52" s="3">
-        <v>451900</v>
+        <v>274000</v>
       </c>
       <c r="G52" s="3">
-        <v>443000</v>
+        <v>69600</v>
       </c>
       <c r="H52" s="3">
-        <v>464100</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>248700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>279500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>260800</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -3080,11 +3200,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3101,8 +3221,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3160,31 +3283,34 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16714800</v>
+        <v>16346200</v>
       </c>
       <c r="E54" s="3">
-        <v>16743600</v>
+        <v>16169500</v>
       </c>
       <c r="F54" s="3">
-        <v>16079000</v>
+        <v>16309200</v>
       </c>
       <c r="G54" s="3">
-        <v>15137600</v>
+        <v>16046200</v>
       </c>
       <c r="H54" s="3">
-        <v>14970300</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>14465500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>14755500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>15122800</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -3198,11 +3324,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
@@ -3219,8 +3345,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3242,8 +3371,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3265,31 +3395,32 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1233900</v>
+        <v>1107500</v>
       </c>
       <c r="E57" s="3">
-        <v>1182900</v>
+        <v>1193600</v>
       </c>
       <c r="F57" s="3">
-        <v>1147500</v>
+        <v>1152200</v>
       </c>
       <c r="G57" s="3">
-        <v>1047800</v>
+        <v>1145100</v>
       </c>
       <c r="H57" s="3">
-        <v>1105400</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>1001300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1089500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1285300</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -3303,11 +3434,11 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3324,31 +3455,34 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1357900</v>
+        <v>965900</v>
       </c>
       <c r="E58" s="3">
-        <v>1381200</v>
+        <v>1313600</v>
       </c>
       <c r="F58" s="3">
-        <v>599200</v>
+        <v>1345300</v>
       </c>
       <c r="G58" s="3">
-        <v>735400</v>
+        <v>598000</v>
       </c>
       <c r="H58" s="3">
-        <v>731000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>702800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>720500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>712700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -3362,11 +3496,11 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3383,31 +3517,34 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>588100</v>
+        <v>644700</v>
       </c>
       <c r="E59" s="3">
-        <v>598100</v>
+        <v>568900</v>
       </c>
       <c r="F59" s="3">
-        <v>556000</v>
+        <v>582600</v>
       </c>
       <c r="G59" s="3">
-        <v>657900</v>
+        <v>194500</v>
       </c>
       <c r="H59" s="3">
-        <v>624700</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>628700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>615700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>626900</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -3421,11 +3558,11 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3442,31 +3579,34 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3179900</v>
+        <v>2718000</v>
       </c>
       <c r="E60" s="3">
-        <v>3162200</v>
+        <v>3076200</v>
       </c>
       <c r="F60" s="3">
-        <v>2302700</v>
+        <v>3080200</v>
       </c>
       <c r="G60" s="3">
-        <v>2441200</v>
+        <v>2298000</v>
       </c>
       <c r="H60" s="3">
-        <v>2461100</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>2332800</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2425800</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2624900</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -3480,11 +3620,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
@@ -3501,31 +3641,34 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3364900</v>
+        <v>3948200</v>
       </c>
       <c r="E61" s="3">
-        <v>3358200</v>
+        <v>3255100</v>
       </c>
       <c r="F61" s="3">
-        <v>4135800</v>
+        <v>3271100</v>
       </c>
       <c r="G61" s="3">
-        <v>3273000</v>
+        <v>4127300</v>
       </c>
       <c r="H61" s="3">
-        <v>3268500</v>
+        <v>3127600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3221600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3205100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3560,31 +3703,34 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1415500</v>
+        <v>478500</v>
       </c>
       <c r="E62" s="3">
-        <v>1377900</v>
+        <v>476800</v>
       </c>
       <c r="F62" s="3">
-        <v>1383400</v>
+        <v>443400</v>
       </c>
       <c r="G62" s="3">
-        <v>1237200</v>
+        <v>459800</v>
       </c>
       <c r="H62" s="3">
-        <v>1298100</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>439200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>468300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>497600</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -3598,11 +3744,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3619,8 +3765,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3678,8 +3827,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3737,8 +3889,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3796,31 +3951,34 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8232800</v>
+        <v>8034800</v>
       </c>
       <c r="E66" s="3">
-        <v>8171900</v>
+        <v>7700600</v>
       </c>
       <c r="F66" s="3">
-        <v>8101000</v>
+        <v>7693400</v>
       </c>
       <c r="G66" s="3">
-        <v>6996700</v>
+        <v>7805900</v>
       </c>
       <c r="H66" s="3">
-        <v>7070900</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>6642700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>6926900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>7124100</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3834,11 +3992,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3">
-        <v>0</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
+        <v>0</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
@@ -3855,8 +4013,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3878,8 +4039,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3937,8 +4099,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3996,8 +4161,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,8 +4205,8 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
+      <c r="P70" s="3">
+        <v>0</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>3</v>
@@ -4055,8 +4223,11 @@
       <c r="U70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4114,31 +4285,34 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5009700</v>
+        <v>5169500</v>
       </c>
       <c r="E72" s="3">
-        <v>5110500</v>
-      </c>
-      <c r="F72" s="3">
-        <v>5025200</v>
+        <v>4846200</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G72" s="3">
-        <v>5056200</v>
+        <v>5014900</v>
       </c>
       <c r="H72" s="3">
-        <v>4925500</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>4831700</v>
+      </c>
+      <c r="I72" s="3">
+        <v>4854800</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4963100</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -4152,11 +4326,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -4173,8 +4347,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4232,8 +4409,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4291,8 +4471,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4350,31 +4533,34 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8482000</v>
+        <v>8035900</v>
       </c>
       <c r="E76" s="3">
-        <v>8571700</v>
+        <v>8205300</v>
       </c>
       <c r="F76" s="3">
-        <v>7978000</v>
+        <v>8349300</v>
       </c>
       <c r="G76" s="3">
-        <v>8140900</v>
+        <v>7961800</v>
       </c>
       <c r="H76" s="3">
-        <v>7899400</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>7779400</v>
+      </c>
+      <c r="I76" s="3">
+        <v>7786000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>7955200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -4388,11 +4574,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
@@ -4409,8 +4595,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4468,49 +4657,52 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4532,44 +4724,47 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>160600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>87500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>126300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>309000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>146200</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>242100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>788900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>357000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4786,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4614,31 +4812,32 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>213800</v>
+        <v>182000</v>
       </c>
       <c r="E83" s="3">
-        <v>209300</v>
+        <v>179000</v>
       </c>
       <c r="F83" s="3">
-        <v>228200</v>
+        <v>178200</v>
       </c>
       <c r="G83" s="3">
-        <v>197200</v>
+        <v>38500</v>
       </c>
       <c r="H83" s="3">
-        <v>369900</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>155900</v>
+      </c>
+      <c r="I83" s="3">
+        <v>163100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>166600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -4649,14 +4848,14 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4673,8 +4872,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4732,8 +4934,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4791,8 +4996,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4850,8 +5058,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4909,8 +5120,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4968,31 +5182,34 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>326700</v>
+        <v>372500</v>
       </c>
       <c r="E89" s="3">
-        <v>94100</v>
+        <v>316100</v>
       </c>
       <c r="F89" s="3">
-        <v>511700</v>
+        <v>91700</v>
       </c>
       <c r="G89" s="3">
-        <v>435300</v>
+        <v>510700</v>
       </c>
       <c r="H89" s="3">
-        <v>461900</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>416000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>299100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>155400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -5003,14 +5220,14 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -5027,8 +5244,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5050,31 +5270,32 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-149000</v>
+        <v>-186300</v>
       </c>
       <c r="E91" s="3">
-        <v>-170000</v>
+        <v>-182100</v>
       </c>
       <c r="F91" s="3">
-        <v>-181000</v>
+        <v>-106800</v>
       </c>
       <c r="G91" s="3">
-        <v>-149000</v>
+        <v>-296200</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-150300</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-147400</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-96700</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5091,8 +5312,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5109,8 +5330,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5168,8 +5392,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5227,31 +5454,34 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-219300</v>
+        <v>-178500</v>
       </c>
       <c r="E94" s="3">
-        <v>-208200</v>
+        <v>-212200</v>
       </c>
       <c r="F94" s="3">
-        <v>-933700</v>
+        <v>-202800</v>
       </c>
       <c r="G94" s="3">
-        <v>-138500</v>
+        <v>-931800</v>
       </c>
       <c r="H94" s="3">
-        <v>-428600</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-132300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-248900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-172800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -5262,14 +5492,14 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5286,8 +5516,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5309,31 +5542,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-289100</v>
+        <v>12300</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>279700</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-280200</v>
+        <v>11600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>276200</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5368,8 +5602,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5427,8 +5664,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5486,8 +5726,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5545,31 +5788,34 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-345600</v>
+        <v>-337900</v>
       </c>
       <c r="E100" s="3">
-        <v>407600</v>
+        <v>-334300</v>
       </c>
       <c r="F100" s="3">
-        <v>572600</v>
+        <v>397000</v>
       </c>
       <c r="G100" s="3">
-        <v>-42100</v>
+        <v>571500</v>
       </c>
       <c r="H100" s="3">
-        <v>41000</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-40200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-314400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>353100</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -5580,14 +5826,14 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -5604,31 +5850,34 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-7800</v>
+        <v>4200</v>
       </c>
       <c r="E101" s="3">
-        <v>6600</v>
+        <v>-9800</v>
       </c>
       <c r="F101" s="3">
-        <v>10000</v>
+        <v>17400</v>
       </c>
       <c r="G101" s="3">
-        <v>4400</v>
+        <v>23500</v>
       </c>
       <c r="H101" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-29400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>32200</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -5639,14 +5888,14 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -5663,31 +5912,34 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-245900</v>
+        <v>-110400</v>
       </c>
       <c r="E102" s="3">
-        <v>300200</v>
+        <v>-237900</v>
       </c>
       <c r="F102" s="3">
-        <v>160600</v>
+        <v>292400</v>
       </c>
       <c r="G102" s="3">
-        <v>259200</v>
+        <v>160300</v>
       </c>
       <c r="H102" s="3">
-        <v>82000</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>247700</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-274000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>353100</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -5698,14 +5950,14 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5720,6 +5972,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,75 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -746,8 +746,11 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -772,21 +775,21 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>2776800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3211800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6605900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3132400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,8 +811,11 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,21 +840,21 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>2358100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2546100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4880100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2316500</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,8 +876,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -896,21 +905,21 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>418700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>665700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1725700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>815900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -932,8 +941,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +968,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,21 +995,21 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
         <v>78600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>71300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>144700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>71600</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1018,8 +1031,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1080,8 +1096,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1106,21 +1125,21 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>78600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>101200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,8 +1161,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1168,8 +1190,8 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1186,8 +1208,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1204,8 +1226,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1225,8 +1250,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1251,21 +1277,21 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
         <v>2756800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2864900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5574300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2661500</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1287,8 +1313,11 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1313,21 +1342,21 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>19900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>346900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1031500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>470900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,8 +1378,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1373,8 +1405,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1399,21 +1432,21 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-35400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-16300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,8 +1468,11 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1461,12 +1497,12 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>767600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,8 +1533,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1523,8 +1562,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1541,8 +1580,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1559,8 +1598,11 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1585,21 +1627,21 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>-15500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>325300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1015200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>461100</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1663,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1647,21 +1692,21 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>-25500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>82100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>218700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>103100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1683,8 +1728,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1745,8 +1793,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1771,21 +1822,21 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>243200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>796500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>358100</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,8 +1858,11 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1833,21 +1887,21 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>-5500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>242100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>788900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>357000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1869,8 +1923,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1931,8 +1988,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1957,8 +2017,8 @@
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1975,8 +2035,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
@@ -1993,8 +2053,11 @@
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2055,8 +2118,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2117,8 +2183,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2143,21 +2212,21 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>35400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>16300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2179,8 +2248,11 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2205,21 +2277,21 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>242100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>788900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>357000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2241,8 +2313,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2303,8 +2378,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2329,21 +2407,21 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>242100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>788900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>357000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,52 +2443,55 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2432,8 +2513,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2456,8 +2540,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2480,35 +2565,36 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2084100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2225100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2243700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2498700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2260400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2011000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1818800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2082800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2521,11 +2607,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
@@ -2542,8 +2628,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2568,8 +2657,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -2583,11 +2672,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2604,35 +2693,38 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1671000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1910600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1998300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1920400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1738700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1796100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1954100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2041500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,11 +2737,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2666,35 +2758,38 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1395600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1552500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1458300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1430600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1335200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1425700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1505500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1597100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,11 +2802,11 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
@@ -2728,35 +2823,38 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E45" s="3">
         <v>48000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>46900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>57600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2772,8 +2870,8 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2790,35 +2888,38 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5171300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5736100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5713100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5860400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5369700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5246600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5325300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5779000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2831,11 +2932,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
@@ -2852,35 +2953,38 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E47" s="3">
         <v>74700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>70700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>70100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>71800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>72000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>76400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>79300</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,11 +2997,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2914,35 +3018,38 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4376200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4165700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4057600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4041400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4122900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3634600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3672500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3657100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,11 +3062,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -2976,35 +3083,38 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5604100</v>
+      </c>
+      <c r="E49" s="3">
         <v>5958100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5818100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5897100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5994300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5088900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5186700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5167300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3017,11 +3127,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3038,8 +3148,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3100,8 +3213,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3162,35 +3278,38 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E52" s="3">
         <v>287800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>315000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>274000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>69600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>248700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>279500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>260800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3203,11 +3322,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3224,8 +3343,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3286,35 +3408,38 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15745900</v>
+      </c>
+      <c r="E54" s="3">
         <v>16346200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16169500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16309200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16046200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14465500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14755500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15122800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,11 +3452,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>0</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
@@ -3348,8 +3473,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3372,8 +3500,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3396,35 +3525,36 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1111900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1107500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1193600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1152200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1145100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1001300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1089500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1285300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3437,11 +3567,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3458,35 +3588,38 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>904900</v>
+      </c>
+      <c r="E58" s="3">
         <v>965900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1313600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1345300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>598000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>702800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>720500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>712700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3499,11 +3632,11 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3520,35 +3653,38 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>182200</v>
+      </c>
+      <c r="E59" s="3">
         <v>644700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>568900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>582600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>194500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>628700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>615700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>626900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3561,11 +3697,11 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3582,35 +3718,38 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2573800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2718000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3076200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3080200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2298000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2332800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2425800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2624900</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,11 +3762,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>0</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
@@ -3644,35 +3783,38 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3809900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3948200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3255100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3271100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4127300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3127600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3221600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3205100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3706,35 +3848,38 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>472100</v>
+      </c>
+      <c r="E62" s="3">
         <v>478500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>476800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>443400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>459800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>439200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>468300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>497600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3747,11 +3892,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3768,8 +3913,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3830,8 +3978,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3892,8 +4043,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3954,35 +4108,38 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7710900</v>
+      </c>
+      <c r="E66" s="3">
         <v>8034800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7700600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7693400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7805900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6642700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6926900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7124100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,11 +4152,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>0</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
@@ -4016,8 +4173,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4040,8 +4200,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4102,8 +4263,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4164,8 +4328,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,8 +4375,8 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3" t="s">
-        <v>3</v>
+      <c r="Q70" s="3">
+        <v>0</v>
       </c>
       <c r="R70" s="3" t="s">
         <v>3</v>
@@ -4226,8 +4393,11 @@
       <c r="V70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4288,35 +4458,38 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4785200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5169500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4846200</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3">
+        <v>4977900</v>
+      </c>
+      <c r="H72" s="3">
         <v>5014900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4831700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4854800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4963100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4329,11 +4502,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
@@ -4350,8 +4523,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4412,8 +4588,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4474,8 +4653,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4536,35 +4718,38 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7791700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8035900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8205300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8349300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7961800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7779400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7786000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7955200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,11 +4762,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
@@ -4598,8 +4783,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4660,52 +4848,55 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4727,8 +4918,11 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4753,21 +4947,21 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>242100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>788900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>357000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4983,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4813,35 +5010,36 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E83" s="3">
         <v>182000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>179000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>178200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>155900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>163100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>166600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4851,14 +5049,14 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4875,8 +5073,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4937,8 +5138,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4999,8 +5203,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5061,8 +5268,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5123,8 +5333,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5185,35 +5398,38 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>421400</v>
+      </c>
+      <c r="E89" s="3">
         <v>372500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>316100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>91700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>510700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>416000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>299100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>155400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5223,14 +5439,14 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
@@ -5247,8 +5463,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5271,35 +5490,36 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-336500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-186300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-182100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-106800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-296200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-150300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-147400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-96700</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -5315,8 +5535,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5333,8 +5553,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5395,8 +5618,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5457,35 +5683,38 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-407900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-178500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-212200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-202800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-931800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-132300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-248900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-172800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5495,14 +5724,14 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5519,8 +5748,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5543,35 +5775,36 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>12300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>279700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5400</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>11600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>276200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -5605,8 +5838,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5667,8 +5903,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5729,8 +5968,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5791,35 +6033,38 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-337900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-334300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>397000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>571500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-40200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-314400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>353100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5829,14 +6074,14 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5853,35 +6098,38 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E101" s="3">
         <v>4200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>17400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>23500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-29400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-38700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>32200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5891,14 +6139,14 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -5915,35 +6163,38 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-110400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-237900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>292400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>160300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>247700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-274000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>353100</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5953,14 +6204,14 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
@@ -5975,6 +6226,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,8 +750,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,21 +782,21 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>2776800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3211800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6605900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3132400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -814,8 +818,11 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -843,21 +850,21 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>2358100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2546100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4880100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2316500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -879,8 +886,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -908,21 +918,21 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>418700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>665700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1725700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>815900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -944,8 +954,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -969,8 +982,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -998,21 +1012,21 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>78600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>71300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>144700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>71600</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1034,8 +1048,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1099,8 +1116,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1128,21 +1148,21 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>78600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>101200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1164,8 +1184,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1193,8 +1216,8 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1211,8 +1234,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
@@ -1229,8 +1252,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1251,8 +1277,9 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1280,21 +1307,21 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>2756800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2864900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5574300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2661500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1343,11 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1345,21 +1375,21 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>19900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>346900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1031500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>470900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1411,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1406,8 +1439,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1435,21 +1469,21 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-35400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-16300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9800</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1471,8 +1505,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1500,12 +1537,12 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>767600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1536,8 +1573,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1565,8 +1605,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1583,8 +1623,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1601,8 +1641,11 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1630,21 +1673,21 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
         <v>-15500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>325300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1015200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>461100</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1666,8 +1709,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1695,21 +1741,21 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>-25500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>82100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>218700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>103100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,8 +1777,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1796,8 +1845,11 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1825,21 +1877,21 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
         <v>10000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>243200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>796500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>358100</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1861,8 +1913,11 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1890,21 +1945,21 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>-5500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>242100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>788900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>357000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +1981,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1991,8 +2049,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2020,8 +2081,8 @@
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2038,8 +2099,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
@@ -2056,8 +2117,11 @@
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2121,8 +2185,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2186,8 +2253,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2215,21 +2285,21 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>35400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>16300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9800</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2251,8 +2321,11 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2280,21 +2353,21 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
         <v>-5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>242100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>788900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>357000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2316,8 +2389,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2381,8 +2457,11 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2410,21 +2489,21 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
         <v>-5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>242100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>788900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>357000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2446,55 +2525,58 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2516,8 +2598,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2541,8 +2626,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2566,38 +2652,39 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1208400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2084100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2225100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2243700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2498700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2260400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2011000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1818800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2082800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,11 +2697,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
@@ -2631,8 +2718,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2660,8 +2750,8 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2675,11 +2765,11 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
@@ -2696,38 +2786,41 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1990900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1671000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1910600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1998300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1920400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1738700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1796100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1954100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2041500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2740,11 +2833,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2761,38 +2854,41 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1553200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1395600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1552500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1458300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1430600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1335200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1425700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1505500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1597100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2805,11 +2901,11 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
@@ -2826,38 +2922,41 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E45" s="3">
         <v>20700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>46900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>57600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2873,8 +2972,8 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2891,38 +2990,41 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4773000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5171300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5736100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5713100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5860400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5369700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5246600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5325300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5779000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,11 +3037,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
@@ -2956,38 +3058,41 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E47" s="3">
         <v>63200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>74700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>70700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>70100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>71800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>72000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>76400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>79300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3000,11 +3105,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3021,38 +3126,41 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4396900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4376200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4165700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4057600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4041400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4122900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3634600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3672500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3657100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,11 +3173,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3086,38 +3194,41 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5719800</v>
+      </c>
+      <c r="E49" s="3">
         <v>5604100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5958100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5818100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5897100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5994300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5088900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5186700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5167300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3130,11 +3241,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3151,8 +3262,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3216,8 +3330,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3281,38 +3398,41 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E52" s="3">
         <v>78700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>287800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>315000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>274000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>69600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>248700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>279500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>260800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,11 +3445,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3346,8 +3466,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3411,38 +3534,41 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15458300</v>
+      </c>
+      <c r="E54" s="3">
         <v>15745900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16346200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16169500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16309200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16046200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14465500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14755500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15122800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,11 +3581,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3">
-        <v>0</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3">
+        <v>0</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
@@ -3476,8 +3602,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3501,8 +3630,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3526,38 +3656,39 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1185700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1111900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1107500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1193600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1152200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1145100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1001300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1089500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1285300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3570,11 +3701,11 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3591,38 +3722,41 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E58" s="3">
         <v>904900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>965900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1313600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1345300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>598000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>702800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>720500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>712700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3635,11 +3769,11 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3656,38 +3790,41 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>591200</v>
+      </c>
+      <c r="E59" s="3">
         <v>182200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>644700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>568900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>582600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>194500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>628700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>615700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>626900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3700,11 +3837,11 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3721,38 +3858,41 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1963900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2573800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2718000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3076200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3080200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2298000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2332800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2425800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2624900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3765,11 +3905,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
@@ -3786,38 +3926,41 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3966700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3809900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3948200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3255100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3271100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4127300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3127600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3221600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3205100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3851,38 +3994,41 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>466900</v>
+      </c>
+      <c r="E62" s="3">
         <v>472100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>478500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>476800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>443400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>459800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>439200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>468300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>497600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3895,11 +4041,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3916,8 +4062,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3981,8 +4130,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4046,8 +4198,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4111,38 +4266,41 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7256800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7710900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8034800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7700600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7693400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7805900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6642700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6926900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7124100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4155,11 +4313,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
+        <v>0</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4334,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4201,8 +4362,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4266,8 +4428,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4331,8 +4496,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4378,8 +4546,8 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3" t="s">
-        <v>3</v>
+      <c r="R70" s="3">
+        <v>0</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>3</v>
@@ -4396,8 +4564,11 @@
       <c r="W70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4461,38 +4632,41 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5043200</v>
+      </c>
+      <c r="E72" s="3">
         <v>4785200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5169500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4846200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4977900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5014900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4831700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4854800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4963100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,11 +4679,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4526,8 +4700,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4591,8 +4768,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4656,8 +4836,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4721,38 +4904,41 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7963700</v>
+      </c>
+      <c r="E76" s="3">
         <v>7791700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8035900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8205300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8349300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7961800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7779400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7786000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7955200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4765,11 +4951,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4786,8 +4972,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4851,55 +5040,58 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4921,8 +5113,11 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4950,21 +5145,21 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
         <v>-5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>242100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>788900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>357000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4986,8 +5181,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5011,38 +5209,39 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E83" s="3">
         <v>9900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>182000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>179000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>178200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>38500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>155900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>163100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>166600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5052,14 +5251,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -5076,8 +5275,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5141,8 +5343,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5206,8 +5411,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5271,8 +5479,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5336,8 +5547,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5401,38 +5615,41 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E89" s="3">
         <v>421400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>372500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>316100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>91700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>510700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>416000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>299100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>155400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5442,14 +5659,14 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5466,8 +5683,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5491,38 +5711,39 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-336500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-186300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-182100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-106800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-296200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-150300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-147400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-96700</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -5538,8 +5759,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5556,8 +5777,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5621,8 +5845,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5686,38 +5913,41 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-196700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-407900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-178500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-212200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-202800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-931800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-132300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-248900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-172800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5727,14 +5957,14 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5751,8 +5981,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5776,38 +6009,39 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>12300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>279700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>11600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>276200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -5841,8 +6075,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5906,8 +6143,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5971,8 +6211,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6036,38 +6279,41 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-820400</v>
+      </c>
+      <c r="E100" s="3">
         <v>41400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-337900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-334300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>397000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>571500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-40200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-314400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>353100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6077,14 +6323,14 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -6101,38 +6347,41 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E101" s="3">
         <v>9900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>17400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>23500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-29400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-38700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>32200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6142,14 +6391,14 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -6166,38 +6415,41 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-967400</v>
+      </c>
+      <c r="E102" s="3">
         <v>18600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-110400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-237900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>292400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>160300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>247700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-274000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>353100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6207,14 +6459,14 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -6229,6 +6481,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,8 +754,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -785,21 +789,21 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>2776800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3211800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6605900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3132400</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,8 +825,11 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,21 +860,21 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>2358100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2546100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4880100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2316500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,8 +896,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -921,21 +931,21 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
         <v>418700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>665700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1725700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>815900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -957,8 +967,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -983,8 +996,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1015,21 +1029,21 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>78600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>71300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>144700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>71600</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1065,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1119,8 +1136,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1151,21 +1171,21 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>78600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>101200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1207,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1219,8 +1242,8 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1237,8 +1260,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1255,8 +1278,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1278,8 +1304,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1310,21 +1337,21 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>2756800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2864900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5574300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2661500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1346,8 +1373,11 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1378,21 +1408,21 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>19900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>346900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1031500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>470900</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,8 +1444,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,8 +1473,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1472,21 +1506,21 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-35400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-16300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1508,8 +1542,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1540,12 +1577,12 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>767600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,8 +1613,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1608,8 +1648,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1626,8 +1666,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1644,8 +1684,11 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1676,21 +1719,21 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-15500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>325300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1015200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>461100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1755,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1744,21 +1790,21 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>-25500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>82100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>218700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>103100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,8 +1826,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1848,8 +1897,11 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1880,21 +1932,21 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>10000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>243200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>796500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>358100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,8 +1968,11 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1948,21 +2003,21 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>242100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>788900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>357000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,8 +2039,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2052,8 +2110,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2084,8 +2145,8 @@
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2102,8 +2163,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
@@ -2120,8 +2181,11 @@
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2188,8 +2252,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2256,8 +2323,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2288,21 +2358,21 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>35400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>16300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2324,8 +2394,11 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2356,21 +2429,21 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>242100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>788900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>357000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,8 +2465,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2460,8 +2536,11 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2492,21 +2571,21 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>242100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>788900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>357000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,58 +2607,61 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2601,8 +2683,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2627,8 +2712,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2653,41 +2739,42 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1539600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1208400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2084100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2225100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2243700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2498700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2260400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2011000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1818800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2082800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,11 +2787,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2721,8 +2808,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2753,8 +2843,8 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2768,11 +2858,11 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
@@ -2789,41 +2879,44 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2059900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1990900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1671000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1910600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1998300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1920400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1738700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1796100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1954100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2041500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,11 +2929,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -2857,41 +2950,44 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1537300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1553200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1395600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1552500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1458300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1430600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1335200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1425700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1505500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1597100</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,11 +3000,11 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
@@ -2925,41 +3021,44 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E45" s="3">
         <v>20500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>46900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57600</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2975,8 +3074,8 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2993,41 +3092,44 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5177900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4773000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5171300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5736100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5713100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5860400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5369700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5246600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5325300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5779000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3040,11 +3142,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -3061,41 +3163,44 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E47" s="3">
         <v>63800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>74700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>70700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>70100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>71800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>72000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>76400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>79300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3108,11 +3213,11 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3129,41 +3234,44 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4582500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4396900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4376200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4165700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4057600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4041400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4122900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3634600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3672500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3657100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,11 +3284,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3197,41 +3305,44 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5938900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5719800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5604100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5958100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5818100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5897100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5994300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5088900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5186700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5167300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3244,11 +3355,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3265,8 +3376,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3333,8 +3447,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3401,41 +3518,44 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>371100</v>
+      </c>
+      <c r="E52" s="3">
         <v>343700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>78700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>287800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>315000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>274000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>248700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>279500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>260800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3448,11 +3568,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3469,8 +3589,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3537,41 +3660,44 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16342900</v>
+      </c>
+      <c r="E54" s="3">
         <v>15458300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15745900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16346200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16169500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16309200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16046200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14465500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14755500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15122800</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,11 +3710,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
+        <v>0</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
@@ -3605,8 +3731,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3631,8 +3760,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3657,41 +3787,42 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1098100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1185700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1111900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1107500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1193600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1152200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1145100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1001300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1089500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1285300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3704,11 +3835,11 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3725,41 +3856,44 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>172600</v>
+      </c>
+      <c r="E58" s="3">
         <v>187000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>904900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>965900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1313600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1345300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>598000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>702800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>720500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>712700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,11 +3906,11 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3793,41 +3927,44 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>627100</v>
+      </c>
+      <c r="E59" s="3">
         <v>591200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>182200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>644700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>568900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>582600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>194500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>628700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>615700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>626900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,11 +3977,11 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3861,41 +3998,44 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1897800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1963900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2573800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2718000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3076200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3080200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2298000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2332800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2425800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2624900</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3908,11 +4048,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3929,41 +4069,44 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4279500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3966700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3809900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3948200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3255100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3271100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4127300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3127600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3221600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3205100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3997,41 +4140,44 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>508500</v>
+      </c>
+      <c r="E62" s="3">
         <v>466900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>472100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>478500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>476800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>443400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>459800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>439200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>468300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>497600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4044,11 +4190,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -4065,8 +4211,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4133,8 +4282,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4201,8 +4353,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4269,41 +4424,44 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7593700</v>
+      </c>
+      <c r="E66" s="3">
         <v>7256800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7710900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8034800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7700600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7693400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7805900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6642700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6926900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7124100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4316,11 +4474,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
+        <v>0</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
@@ -4337,8 +4495,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4363,8 +4524,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4431,8 +4593,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4499,8 +4664,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4549,8 +4717,8 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-      <c r="S70" s="3" t="s">
-        <v>3</v>
+      <c r="S70" s="3">
+        <v>0</v>
       </c>
       <c r="T70" s="3" t="s">
         <v>3</v>
@@ -4567,8 +4735,11 @@
       <c r="X70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4635,41 +4806,44 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5239000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5043200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4785200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5169500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4846200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4977900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5014900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4831700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4854800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4963100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4682,11 +4856,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4703,8 +4877,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4771,8 +4948,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4839,8 +5019,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4907,41 +5090,44 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8495600</v>
+      </c>
+      <c r="E76" s="3">
         <v>7963700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7791700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8035900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8205300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8349300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7961800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7779400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7786000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7955200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4954,11 +5140,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4975,8 +5161,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5043,58 +5232,61 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5116,8 +5308,11 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5148,21 +5343,21 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>242100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>788900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>357000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5184,8 +5379,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5210,41 +5408,42 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E83" s="3">
         <v>200700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>182000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>179000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>178200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>155900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>163100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>166600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5254,14 +5453,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -5278,8 +5477,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5346,8 +5548,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5414,8 +5619,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5482,8 +5690,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5550,8 +5761,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5618,41 +5832,44 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>297100</v>
+      </c>
+      <c r="E89" s="3">
         <v>23800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>421400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>372500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>316100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>91700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>510700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>416000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>299100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>155400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5662,14 +5879,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5686,8 +5903,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5712,41 +5932,42 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-177300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-96200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-336500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-186300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-182100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-106800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-296200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-150300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-147400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-96700</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5762,8 +5983,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5780,8 +6001,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5848,8 +6072,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5916,41 +6143,44 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-192600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-196700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-407900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-178500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-212200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-202800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-931800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-132300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-248900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-172800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5960,14 +6190,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5984,8 +6214,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6010,41 +6243,42 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>319400</v>
+      </c>
+      <c r="E96" s="3">
         <v>25900</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>12300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>279700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>11600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>276200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>5400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -6078,8 +6312,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6146,8 +6383,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6214,8 +6454,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6282,41 +6525,44 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-820400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>41400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-337900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-334300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>397000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>571500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-40200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-314400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>353100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6326,14 +6572,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -6350,41 +6596,44 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E101" s="3">
         <v>6500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>17400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>23500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-29400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-38700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>32200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6394,14 +6643,14 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6418,41 +6667,44 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>226700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-967400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-110400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-237900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>292400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>160300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>247700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-274000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>353100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6462,14 +6714,14 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -6484,6 +6736,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,90 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -761,8 +761,11 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -799,21 +802,21 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
         <v>2776800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3211800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6605900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3132400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,8 +838,11 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,21 +879,21 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>2358100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2546100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4880100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2316500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,8 +915,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,21 +956,21 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
         <v>418700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>665700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1725700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>815900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -983,8 +992,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1011,8 +1023,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1049,21 +1062,21 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3">
         <v>78600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>71300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>144700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>71600</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1085,8 +1098,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1159,8 +1175,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1197,21 +1216,21 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>78600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>101200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1233,8 +1252,11 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1271,8 +1293,8 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1289,8 +1311,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
@@ -1307,8 +1329,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1332,8 +1357,9 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1370,21 +1396,21 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3">
         <v>2756800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2864900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5574300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2661500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,8 +1432,11 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1444,21 +1473,21 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>19900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>346900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1031500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>470900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,8 +1509,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1508,8 +1540,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1546,21 +1579,21 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-35400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-16300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1615,11 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1620,12 +1656,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>767600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,8 +1692,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1694,8 +1733,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1712,8 +1751,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1730,8 +1769,11 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1768,21 +1810,21 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3">
         <v>-15500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>325300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1015200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>461100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1804,8 +1846,11 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1842,21 +1887,21 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>-25500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>82100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>218700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>103100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,8 +1923,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1952,8 +2000,11 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1990,21 +2041,21 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3">
         <v>10000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>243200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>796500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>358100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,8 +2077,11 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2064,21 +2118,21 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3">
         <v>-5500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>242100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>788900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>357000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2100,8 +2154,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2174,8 +2231,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2212,8 +2272,8 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2230,8 +2290,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
@@ -2248,8 +2308,11 @@
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2322,8 +2385,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2396,8 +2462,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2434,21 +2503,21 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>35400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>21600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>16300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2539,11 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2508,21 +2580,21 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3">
         <v>-5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>242100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>788900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>357000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,8 +2616,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2618,8 +2693,11 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2656,21 +2734,21 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3">
         <v>-5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>242100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>788900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>357000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,64 +2770,67 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2771,8 +2852,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2799,8 +2883,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2827,47 +2912,48 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2569000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2291400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1539600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1208400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2084100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2225100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2243700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2498700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2260400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2011000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1818800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2082800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,11 +2966,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2901,8 +2987,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2939,8 +3028,8 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2954,11 +3043,11 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
@@ -2975,47 +3064,50 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1745900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1932400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2059900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1990900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1671000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1910600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1998300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1920400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1738700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1796100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1954100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2041500</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,11 +3120,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -3049,47 +3141,50 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1340800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1535800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1537300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1553200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1395600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1552500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1458300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1430600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1335200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1425700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1505500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1597100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3102,11 +3197,11 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
@@ -3123,47 +3218,50 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E45" s="3">
         <v>24600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>46900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>57600</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -3179,8 +3277,8 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -3197,47 +3295,50 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5665100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5784300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5177900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4773000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5171300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5736100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5713100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5860400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5369700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5246600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5325300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5779000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3250,11 +3351,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
@@ -3271,47 +3372,50 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E47" s="3">
         <v>48100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>74700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>70700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>70100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>71800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>72000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>76400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>79300</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,11 +3428,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3345,47 +3449,50 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4620200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4532400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4582500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4396900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4376200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4165700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4057600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4041400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4122900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3634600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3672500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3657100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3398,11 +3505,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3419,47 +3526,50 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5837700</v>
+      </c>
+      <c r="E49" s="3">
         <v>5900500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5938900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5719800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5604100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5958100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5818100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5897100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5994300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5088900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5186700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5167300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,11 +3582,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3493,8 +3603,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3567,8 +3680,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3641,47 +3757,50 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E52" s="3">
         <v>342600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>371100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>343700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>78700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>287800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>315000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>274000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>69600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>248700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>279500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>260800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,11 +3813,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3715,8 +3834,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3789,47 +3911,50 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16725400</v>
+      </c>
+      <c r="E54" s="3">
         <v>16775800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16342900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15458300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15745900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16346200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16169500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16309200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16046200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14465500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14755500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15122800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3842,11 +3967,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T54" s="3">
-        <v>0</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3">
+        <v>0</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
@@ -3863,8 +3988,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3891,8 +4019,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3919,47 +4048,48 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1140100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1039500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1098100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1185700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1111900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1107500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1193600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1152200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1145100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1001300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1089500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1285300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3972,11 +4102,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3993,47 +4123,50 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>887600</v>
+      </c>
+      <c r="E58" s="3">
         <v>166600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>172600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>187000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>904900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>965900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1313600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1345300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>598000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>702800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>720500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>712700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4046,11 +4179,11 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4067,47 +4200,50 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>206600</v>
+      </c>
+      <c r="E59" s="3">
         <v>677000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>627100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>591200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>182200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>644700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>568900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>582600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>194500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>628700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>615700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>626900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4120,11 +4256,11 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -4141,47 +4277,50 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2653500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1883100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1897800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1963900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2573800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2718000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3076200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3080200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2298000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2332800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2425800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2624900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4194,11 +4333,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -4215,47 +4354,50 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4464000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4826900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4279500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3966700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3809900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3948200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3255100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3271100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4127300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3127600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3221600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3205100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4289,47 +4431,50 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>448500</v>
+      </c>
+      <c r="E62" s="3">
         <v>437600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>508500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>466900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>472100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>478500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>476800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>443400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>459800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>439200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>468300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>497600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,11 +4487,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4363,8 +4508,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4437,8 +4585,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4511,8 +4662,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4585,47 +4739,50 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8468900</v>
+      </c>
+      <c r="E66" s="3">
         <v>8067600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7593700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7256800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7710900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8034800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7700600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7693400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7805900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6642700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6926900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7124100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4638,11 +4795,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3">
+        <v>0</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
@@ -4659,8 +4816,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4687,8 +4847,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4761,8 +4922,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4835,8 +4999,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4891,8 +5058,8 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3" t="s">
-        <v>3</v>
+      <c r="U70" s="3">
+        <v>0</v>
       </c>
       <c r="V70" s="3" t="s">
         <v>3</v>
@@ -4909,8 +5076,11 @@
       <c r="Z70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4983,47 +5153,50 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5136800</v>
+      </c>
+      <c r="E72" s="3">
         <v>5251700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5239000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5043200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4785200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5169500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4846200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4977900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5014900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4831700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4854800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4963100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5036,11 +5209,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -5057,8 +5230,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5131,8 +5307,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5205,8 +5384,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5279,47 +5461,50 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8034500</v>
+      </c>
+      <c r="E76" s="3">
         <v>8472400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8495600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7963700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7791700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8035900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8205300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8349300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7961800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7779400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7786000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7955200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5332,11 +5517,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -5353,8 +5538,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5427,64 +5615,67 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5506,8 +5697,11 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5544,21 +5738,21 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3">
         <v>-5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>242100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>788900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>357000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5580,8 +5774,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5608,47 +5805,48 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>226700</v>
+      </c>
+      <c r="E83" s="3">
         <v>210800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>210000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>182000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>179000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>178200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>155900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>163100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>166600</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5658,14 +5856,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5682,8 +5880,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5756,8 +5957,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5830,8 +6034,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5904,8 +6111,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5978,8 +6188,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6052,47 +6265,50 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>497800</v>
+      </c>
+      <c r="E89" s="3">
         <v>349600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>297100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>421400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>372500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>316100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>91700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>510700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>416000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>299100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>155400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,14 +6318,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -6126,8 +6342,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6154,47 +6373,48 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-311100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-153700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-177300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-336500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-186300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-182100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-106800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-296200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-150300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-147400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-96700</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -6210,8 +6430,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6228,8 +6448,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6302,8 +6525,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6376,47 +6602,50 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-186700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-130200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-192600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-196700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-407900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-178500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-212200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-202800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-931800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-132300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-248900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-172800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6426,14 +6655,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6450,8 +6679,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6478,8 +6710,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6487,38 +6720,38 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>319400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>25900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>12300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>279700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>11600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>276200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>5400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -6552,8 +6785,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6626,8 +6862,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6700,8 +6939,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6774,47 +7016,50 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E100" s="3">
         <v>524500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>68100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-820400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>41400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-337900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-334300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>397000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>571500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-40200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-314400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>353100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6824,14 +7069,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6848,47 +7093,50 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36200</v>
+      </c>
+      <c r="E101" s="3">
         <v>33500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>17400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>23500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-38700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>32200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6898,14 +7146,14 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6922,47 +7170,50 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>275900</v>
+      </c>
+      <c r="E102" s="3">
         <v>753300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>226700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-967400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-110400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-237900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>292400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>160300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>247700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-274000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>353100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6972,14 +7223,14 @@
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6994,6 +7245,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -764,8 +765,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,21 +809,21 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2776800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3211800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6605900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3132400</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,8 +845,11 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,21 +889,21 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>2358100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2546100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4880100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2316500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,8 +925,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,21 +969,21 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>418700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>665700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1725700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>815900</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -995,8 +1005,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1024,8 +1037,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,21 +1079,21 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
         <v>78600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>71300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>144700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>71600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,8 +1115,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1178,8 +1195,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1219,21 +1239,21 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>78600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>101200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1255,8 +1275,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1296,8 +1319,8 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1314,8 +1337,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
@@ -1332,8 +1355,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1358,8 +1384,9 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1399,21 +1426,21 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3">
         <v>2756800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2864900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5574300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2661500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,8 +1462,11 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1476,21 +1506,21 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>19900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>346900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1031500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>470900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,8 +1542,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1541,8 +1574,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1582,21 +1616,21 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-21600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-16300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,8 +1652,11 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1659,12 +1696,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>767600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,8 +1732,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1736,8 +1776,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1754,8 +1794,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1772,8 +1812,11 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1813,21 +1856,21 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>325300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1015200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>461100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1849,8 +1892,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1890,21 +1936,21 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>82100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>218700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>103100</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +1972,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2003,8 +2052,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2044,21 +2096,21 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3">
         <v>10000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>243200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>796500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>358100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,8 +2132,11 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2121,21 +2176,21 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>242100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>788900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>357000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2157,8 +2212,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2234,8 +2292,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2275,8 +2336,8 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2293,8 +2354,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
@@ -2311,8 +2372,11 @@
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2388,8 +2452,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2465,8 +2532,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2506,21 +2576,21 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>35400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>21600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>16300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,8 +2612,11 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2583,21 +2656,21 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>242100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>788900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>357000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2619,8 +2692,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2696,8 +2772,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2737,21 +2816,21 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>242100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>788900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>357000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,67 +2852,70 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +2937,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2884,8 +2969,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2913,50 +2999,51 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1994600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2569000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2291400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1539600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1208400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2084100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2225100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2243700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2498700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2260400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2011000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1818800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2082800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2969,11 +3056,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3">
+        <v>0</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
@@ -2990,8 +3077,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3031,8 +3121,8 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -3046,11 +3136,11 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
@@ -3067,50 +3157,53 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2059300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1745900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1932400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2059900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1990900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1671000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1910600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1998300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1920400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1738700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1796100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1954100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2041500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3123,11 +3216,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
@@ -3144,50 +3237,53 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1497800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1340800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1535800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1537300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1553200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1395600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1552500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1458300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1430600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1335200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1425700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1505500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1597100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,11 +3296,11 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
@@ -3221,50 +3317,53 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E45" s="3">
         <v>9400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>46900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>57600</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3280,8 +3379,8 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="V45" s="3">
+        <v>0</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
@@ -3298,50 +3397,53 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5576800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5665100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5784300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5177900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4773000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5171300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5736100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5713100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5860400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5369700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5246600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5325300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5779000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,11 +3456,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
@@ -3375,50 +3477,53 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E47" s="3">
         <v>49300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>63200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>74700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>70700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>70100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>71800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>76400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>79300</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3431,11 +3536,11 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3452,50 +3557,53 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4527000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4620200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4532400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4582500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4396900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4376200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4165700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4057600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4041400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4122900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3634600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3672500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3657100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3508,11 +3616,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3529,50 +3637,53 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5753300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5837700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5900500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5938900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5719800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5604100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5958100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5818100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5897100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5994300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5088900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5186700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5167300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,11 +3696,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3606,8 +3717,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3683,8 +3797,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3760,50 +3877,53 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>327700</v>
+      </c>
+      <c r="E52" s="3">
         <v>86900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>342600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>371100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>343700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>78700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>287800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>315000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>274000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>69600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>248700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>279500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>260800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3816,11 +3936,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3837,8 +3957,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3914,50 +4037,53 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16396500</v>
+      </c>
+      <c r="E54" s="3">
         <v>16725400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16775800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16342900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15458300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15745900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16346200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16169500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16309200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16046200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14465500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14755500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15122800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,11 +4096,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3">
-        <v>0</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
+        <v>0</v>
       </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
@@ -3991,8 +4117,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4020,8 +4149,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4049,50 +4179,51 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1228900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1140100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1039500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1098100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1185700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1111900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1107500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1193600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1152200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1145100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1001300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1089500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1285300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4105,11 +4236,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -4126,50 +4257,53 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>536500</v>
+      </c>
+      <c r="E58" s="3">
         <v>887600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>166600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>172600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>187000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>904900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>965900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1313600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1345300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>598000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>702800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>720500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>712700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,11 +4316,11 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4203,50 +4337,53 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>715000</v>
+      </c>
+      <c r="E59" s="3">
         <v>206600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>677000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>627100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>591200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>182200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>644700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>568900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>582600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>194500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>628700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>615700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>626900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4259,11 +4396,11 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
@@ -4280,50 +4417,53 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2480300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2653500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1883100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1897800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1963900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2573800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2718000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3076200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3080200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2298000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2332800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2425800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2624900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4336,11 +4476,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
@@ -4357,50 +4497,53 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4391300</v>
+      </c>
+      <c r="E61" s="3">
         <v>4464000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4826900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4279500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3966700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3809900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3948200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3255100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3271100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4127300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3127600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3221600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3205100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4434,50 +4577,53 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>426700</v>
+      </c>
+      <c r="E62" s="3">
         <v>448500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>437600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>508500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>466900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>472100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>478500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>476800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>443400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>459800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>439200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>468300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>497600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4490,11 +4636,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -4511,8 +4657,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4588,8 +4737,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4665,8 +4817,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4742,50 +4897,53 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8163600</v>
+      </c>
+      <c r="E66" s="3">
         <v>8468900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8067600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7593700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7256800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7710900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8034800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7700600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7693400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7805900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6642700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6926900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7124100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4798,11 +4956,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3">
-        <v>0</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
+        <v>0</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
@@ -4819,8 +4977,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4848,8 +5009,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4925,8 +5087,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5002,8 +5167,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5061,8 +5229,8 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-      <c r="V70" s="3" t="s">
-        <v>3</v>
+      <c r="V70" s="3">
+        <v>0</v>
       </c>
       <c r="W70" s="3" t="s">
         <v>3</v>
@@ -5079,8 +5247,11 @@
       <c r="AA70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5156,50 +5327,53 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5079400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5136800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5251700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5239000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5043200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4785200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5169500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4846200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4977900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5014900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4831700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4854800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4963100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5212,11 +5386,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -5233,8 +5407,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5310,8 +5487,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5387,8 +5567,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5464,50 +5647,53 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8021300</v>
+      </c>
+      <c r="E76" s="3">
         <v>8034500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8472400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8495600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7963700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7791700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8035900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8205300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8349300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7961800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7779400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7786000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7955200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,11 +5706,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -5541,8 +5727,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5618,67 +5807,70 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5700,8 +5892,11 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5741,21 +5936,21 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>242100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>788900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>357000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5777,8 +5972,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5806,50 +6004,51 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E83" s="3">
         <v>226700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>210800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>210000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>182000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>179000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>178200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>155900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>163100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>166600</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5859,14 +6058,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5883,8 +6082,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5960,8 +6162,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6037,8 +6242,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6114,8 +6322,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6191,8 +6402,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6268,50 +6482,53 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E89" s="3">
         <v>497800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>349600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>297100</v>
       </c>
-      <c r="G89" s="3">
-        <v>23800</v>
-      </c>
       <c r="H89" s="3">
+        <v>24100</v>
+      </c>
+      <c r="I89" s="3">
         <v>421400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>372500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>316100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>91700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>510700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>416000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>299100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>155400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6321,14 +6538,14 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -6345,8 +6562,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6374,50 +6594,51 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-85900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-311100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-153700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-177300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-96200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-95900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-336500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-186300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-182100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-106800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-296200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-147400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-96700</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -6433,8 +6654,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6451,8 +6672,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6528,8 +6752,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6605,50 +6832,53 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-163800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-186700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-130200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-192600</v>
       </c>
-      <c r="G94" s="3">
-        <v>-196700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-197300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-407900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-178500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-212200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-202800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-931800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-132300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-248900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-172800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6658,14 +6888,14 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6682,8 +6912,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6711,50 +6944,51 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>319400</v>
       </c>
-      <c r="G96" s="3">
-        <v>25900</v>
-      </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>12300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>279700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>11600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>276200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>5400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6788,8 +7022,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6865,8 +7102,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6942,8 +7182,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7019,50 +7262,53 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-385000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-37600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>524500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>68100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-820400</v>
-      </c>
       <c r="H100" s="3">
+        <v>-820700</v>
+      </c>
+      <c r="I100" s="3">
         <v>41400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-337900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-334300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>397000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>571500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-40200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-314400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>353100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7072,14 +7318,14 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -7096,50 +7342,53 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-36200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>33500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>17400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>23500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-29400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-38700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>32200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7149,14 +7398,14 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -7173,50 +7422,53 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-528800</v>
+      </c>
+      <c r="E102" s="3">
         <v>275900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>753300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>226700</v>
       </c>
-      <c r="G102" s="3">
-        <v>-967400</v>
-      </c>
       <c r="H102" s="3">
+        <v>-967800</v>
+      </c>
+      <c r="I102" s="3">
         <v>18600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-110400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-237900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>292400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>160300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>247700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-274000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>353100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7226,14 +7478,14 @@
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -7248,6 +7500,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
